--- a/catalogos/CATALOGO_LINEAS_VALIDAS_21082026.xlsx
+++ b/catalogos/CATALOGO_LINEAS_VALIDAS_21082026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12570" tabRatio="635"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12570" tabRatio="635" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Adquisición" sheetId="3" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="43">
   <si>
     <t>Autoproducción</t>
   </si>
@@ -349,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -445,9 +445,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -567,6 +564,121 @@
   </cellStyles>
   <dxfs count="62">
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
       <border outline="0">
         <left style="thin">
@@ -1516,121 +1628,6 @@
         <name val="Noto Sans"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill patternType="none">
@@ -2470,60 +2467,60 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Tabla1" displayName="Tabla1" ref="A1:G48" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41" tableBorderDxfId="39" totalsRowBorderDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Tabla1" displayName="Tabla1" ref="A1:G50" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41" tableBorderDxfId="39" totalsRowBorderDxfId="38">
   <tableColumns count="7">
     <tableColumn id="1" name="esquema" dataDxfId="37"/>
     <tableColumn id="2" name="modalidad" dataDxfId="36"/>
     <tableColumn id="3" name="linea_de_apoyo" dataDxfId="35"/>
-    <tableColumn id="7" name="uma_max" dataDxfId="34"/>
-    <tableColumn id="4" name="uma_la" dataDxfId="33"/>
-    <tableColumn id="5" name="linea_complementaria" dataDxfId="32"/>
-    <tableColumn id="6" name="uma_lc" dataDxfId="31"/>
+    <tableColumn id="7" name="uma_max" dataDxfId="2"/>
+    <tableColumn id="4" name="uma_la" dataDxfId="0"/>
+    <tableColumn id="5" name="linea_complementaria" dataDxfId="1"/>
+    <tableColumn id="6" name="uma_lc" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabla2" displayName="Tabla2" ref="A1:G57" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabla2" displayName="Tabla2" ref="A1:G57" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
   <tableColumns count="7">
-    <tableColumn id="1" name="esquema" dataDxfId="28"/>
-    <tableColumn id="2" name="modalidad" dataDxfId="27"/>
-    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="26"/>
-    <tableColumn id="8" name="uma_max" dataDxfId="25"/>
-    <tableColumn id="4" name="uma_la" dataDxfId="24"/>
-    <tableColumn id="5" name="linea_complementaria" dataDxfId="23"/>
-    <tableColumn id="6" name="uma_lc" dataDxfId="22"/>
+    <tableColumn id="1" name="esquema" dataDxfId="31"/>
+    <tableColumn id="2" name="modalidad" dataDxfId="30"/>
+    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="29"/>
+    <tableColumn id="8" name="uma_max" dataDxfId="28"/>
+    <tableColumn id="4" name="uma_la" dataDxfId="27"/>
+    <tableColumn id="5" name="linea_complementaria" dataDxfId="26"/>
+    <tableColumn id="6" name="uma_lc" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tabla5" displayName="Tabla5" ref="A1:G2" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tabla5" displayName="Tabla5" ref="A1:G2" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23" tableBorderDxfId="22" totalsRowBorderDxfId="21">
   <tableColumns count="7">
-    <tableColumn id="1" name="esquema" dataDxfId="17"/>
-    <tableColumn id="2" name="modalidad" dataDxfId="16"/>
-    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="15"/>
-    <tableColumn id="7" name="uma_max" dataDxfId="14"/>
-    <tableColumn id="4" name="uma_la" dataDxfId="13"/>
-    <tableColumn id="5" name="linea_complementaria" dataDxfId="12"/>
-    <tableColumn id="6" name="uma_lc" dataDxfId="11"/>
+    <tableColumn id="1" name="esquema" dataDxfId="20"/>
+    <tableColumn id="2" name="modalidad" dataDxfId="19"/>
+    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="18"/>
+    <tableColumn id="7" name="uma_max" dataDxfId="17"/>
+    <tableColumn id="4" name="uma_la" dataDxfId="16"/>
+    <tableColumn id="5" name="linea_complementaria" dataDxfId="15"/>
+    <tableColumn id="6" name="uma_lc" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Tabla6" displayName="Tabla6" ref="A1:G3" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Tabla6" displayName="Tabla6" ref="A1:G3" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <tableColumns count="7">
-    <tableColumn id="1" name="esquema" dataDxfId="6"/>
-    <tableColumn id="2" name="modalidad" dataDxfId="5"/>
-    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="4"/>
-    <tableColumn id="7" name="uma_max" dataDxfId="3"/>
-    <tableColumn id="4" name="uma_la" dataDxfId="2"/>
-    <tableColumn id="5" name="linea_complementaria" dataDxfId="1"/>
-    <tableColumn id="6" name="uma_lc" dataDxfId="0"/>
+    <tableColumn id="1" name="esquema" dataDxfId="9"/>
+    <tableColumn id="2" name="modalidad" dataDxfId="8"/>
+    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="7"/>
+    <tableColumn id="7" name="uma_max" dataDxfId="6"/>
+    <tableColumn id="4" name="uma_la" dataDxfId="5"/>
+    <tableColumn id="5" name="linea_complementaria" dataDxfId="4"/>
+    <tableColumn id="6" name="uma_lc" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2752,7 +2749,7 @@
       <c r="A1" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="73" t="s">
         <v>30</v>
       </c>
       <c r="C1" s="18" t="s">
@@ -2781,7 +2778,7 @@
       <c r="C2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="39">
+      <c r="D2" s="38">
         <v>190</v>
       </c>
       <c r="E2" s="13">
@@ -2800,7 +2797,7 @@
       <c r="C3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="39">
+      <c r="D3" s="38">
         <v>170</v>
       </c>
       <c r="E3" s="13">
@@ -2819,7 +2816,7 @@
       <c r="C4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="73">
+      <c r="D4" s="72">
         <v>158</v>
       </c>
       <c r="E4" s="13">
@@ -2838,7 +2835,7 @@
       <c r="C5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="39">
+      <c r="D5" s="38">
         <v>140</v>
       </c>
       <c r="E5" s="13">
@@ -2857,7 +2854,7 @@
       <c r="C6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="38">
         <v>391</v>
       </c>
       <c r="E6" s="13">
@@ -2880,7 +2877,7 @@
       <c r="C7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="38">
         <v>391</v>
       </c>
       <c r="E7" s="13">
@@ -2903,7 +2900,7 @@
       <c r="C8" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="38">
         <v>391</v>
       </c>
       <c r="E8" s="13">
@@ -2926,7 +2923,7 @@
       <c r="C9" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="38">
         <v>391</v>
       </c>
       <c r="E9" s="13">
@@ -2949,7 +2946,7 @@
       <c r="C10" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="38">
         <v>391</v>
       </c>
       <c r="E10" s="13">
@@ -2972,7 +2969,7 @@
       <c r="C11" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="38">
         <v>391</v>
       </c>
       <c r="E11" s="13">
@@ -2995,7 +2992,7 @@
       <c r="C12" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="39">
+      <c r="D12" s="38">
         <v>391</v>
       </c>
       <c r="E12" s="13">
@@ -3018,7 +3015,7 @@
       <c r="C13" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="38">
         <v>391</v>
       </c>
       <c r="E13" s="13">
@@ -3041,7 +3038,7 @@
       <c r="C14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="39">
+      <c r="D14" s="38">
         <v>391</v>
       </c>
       <c r="E14" s="13">
@@ -3071,13 +3068,14 @@
   <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="19.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="60.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.44140625" style="1"/>
+    <col min="5" max="5" width="7.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.45">
@@ -3087,19 +3085,19 @@
       <c r="B1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="49" t="s">
+      <c r="E1" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="49" t="s">
+      <c r="G1" s="48" t="s">
         <v>36</v>
       </c>
     </row>
@@ -3113,7 +3111,7 @@
       <c r="C2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="45">
+      <c r="D2" s="44">
         <v>155</v>
       </c>
       <c r="E2" s="31">
@@ -3136,7 +3134,7 @@
       <c r="C3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="45">
+      <c r="D3" s="44">
         <v>155</v>
       </c>
       <c r="E3" s="31">
@@ -3159,7 +3157,7 @@
       <c r="C4" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="45">
+      <c r="D4" s="44">
         <v>155</v>
       </c>
       <c r="E4" s="31">
@@ -3182,7 +3180,7 @@
       <c r="C5" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="45">
+      <c r="D5" s="44">
         <v>155</v>
       </c>
       <c r="E5" s="31">
@@ -3205,7 +3203,7 @@
       <c r="C6" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="45">
+      <c r="D6" s="44">
         <v>155</v>
       </c>
       <c r="E6" s="31">
@@ -3228,7 +3226,7 @@
       <c r="C7" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="45">
+      <c r="D7" s="44">
         <v>155</v>
       </c>
       <c r="E7" s="31">
@@ -3242,48 +3240,48 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="51" t="s">
+      <c r="B8" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="54">
+      <c r="D8" s="53">
         <v>155</v>
       </c>
-      <c r="E8" s="52">
+      <c r="E8" s="51">
         <v>25</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="53">
+      <c r="G8" s="52">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="51" t="s">
+      <c r="B9" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="54">
+      <c r="D9" s="53">
         <v>155</v>
       </c>
-      <c r="E9" s="52">
+      <c r="E9" s="51">
         <v>25</v>
       </c>
-      <c r="F9" s="50" t="s">
+      <c r="F9" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="53">
+      <c r="G9" s="52">
         <v>20</v>
       </c>
     </row>
@@ -3297,7 +3295,7 @@
       <c r="C10" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="45">
+      <c r="D10" s="44">
         <v>180</v>
       </c>
       <c r="E10" s="31">
@@ -3320,7 +3318,7 @@
       <c r="C11" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="44">
         <v>180</v>
       </c>
       <c r="E11" s="31">
@@ -3343,7 +3341,7 @@
       <c r="C12" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="45">
+      <c r="D12" s="44">
         <v>180</v>
       </c>
       <c r="E12" s="31">
@@ -3366,7 +3364,7 @@
       <c r="C13" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="45">
+      <c r="D13" s="44">
         <v>180</v>
       </c>
       <c r="E13" s="31">
@@ -3389,7 +3387,7 @@
       <c r="C14" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="45">
+      <c r="D14" s="44">
         <v>180</v>
       </c>
       <c r="E14" s="31">
@@ -3412,7 +3410,7 @@
       <c r="C15" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="45">
+      <c r="D15" s="44">
         <v>180</v>
       </c>
       <c r="E15" s="31">
@@ -3426,71 +3424,71 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A16" s="50" t="s">
+      <c r="A16" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16" s="51" t="s">
+      <c r="B16" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="54">
+      <c r="D16" s="53">
         <v>180</v>
       </c>
-      <c r="E16" s="52">
+      <c r="E16" s="51">
         <v>50</v>
       </c>
-      <c r="F16" s="50" t="s">
+      <c r="F16" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="53">
+      <c r="G16" s="52">
         <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" s="50" t="s">
+      <c r="A17" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" s="51" t="s">
+      <c r="B17" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="54">
+      <c r="D17" s="53">
         <v>180</v>
       </c>
-      <c r="E17" s="52">
+      <c r="E17" s="51">
         <v>50</v>
       </c>
-      <c r="F17" s="50" t="s">
+      <c r="F17" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="53">
+      <c r="G17" s="52">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A18" s="50" t="s">
+      <c r="A18" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="51" t="s">
+      <c r="B18" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="54">
+      <c r="D18" s="53">
         <v>180</v>
       </c>
-      <c r="E18" s="52">
+      <c r="E18" s="51">
         <v>50</v>
       </c>
-      <c r="F18" s="50" t="s">
+      <c r="F18" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="G18" s="53">
+      <c r="G18" s="52">
         <v>16</v>
       </c>
     </row>
@@ -3504,7 +3502,7 @@
       <c r="C19" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="45">
+      <c r="D19" s="44">
         <v>200</v>
       </c>
       <c r="E19" s="31">
@@ -3527,7 +3525,7 @@
       <c r="C20" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="45">
+      <c r="D20" s="44">
         <v>200</v>
       </c>
       <c r="E20" s="31">
@@ -3550,7 +3548,7 @@
       <c r="C21" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="45">
+      <c r="D21" s="44">
         <v>200</v>
       </c>
       <c r="E21" s="31">
@@ -3573,7 +3571,7 @@
       <c r="C22" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="45">
+      <c r="D22" s="44">
         <v>200</v>
       </c>
       <c r="E22" s="31">
@@ -3596,7 +3594,7 @@
       <c r="C23" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="45">
+      <c r="D23" s="44">
         <v>200</v>
       </c>
       <c r="E23" s="31">
@@ -3610,48 +3608,48 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A24" s="50" t="s">
+      <c r="A24" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="51" t="s">
+      <c r="B24" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="54">
+      <c r="D24" s="53">
         <v>200</v>
       </c>
-      <c r="E24" s="52">
+      <c r="E24" s="51">
         <v>100</v>
       </c>
-      <c r="F24" s="50" t="s">
+      <c r="F24" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="G24" s="53">
+      <c r="G24" s="52">
         <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A25" s="50" t="s">
+      <c r="A25" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C25" s="51" t="s">
+      <c r="B25" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="54">
+      <c r="D25" s="53">
         <v>200</v>
       </c>
-      <c r="E25" s="52">
+      <c r="E25" s="51">
         <v>100</v>
       </c>
-      <c r="F25" s="50" t="s">
+      <c r="F25" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="53">
+      <c r="G25" s="52">
         <v>20</v>
       </c>
     </row>
@@ -3665,7 +3663,7 @@
       <c r="C26" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="45">
+      <c r="D26" s="44">
         <v>187</v>
       </c>
       <c r="E26" s="31">
@@ -3688,7 +3686,7 @@
       <c r="C27" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="45">
+      <c r="D27" s="44">
         <v>187</v>
       </c>
       <c r="E27" s="31">
@@ -3711,7 +3709,7 @@
       <c r="C28" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="45">
+      <c r="D28" s="44">
         <v>187</v>
       </c>
       <c r="E28" s="31">
@@ -3734,7 +3732,7 @@
       <c r="C29" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="45">
+      <c r="D29" s="44">
         <v>187</v>
       </c>
       <c r="E29" s="31">
@@ -3748,71 +3746,71 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A30" s="50" t="s">
+      <c r="A30" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="51" t="s">
+      <c r="B30" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="54">
+      <c r="D30" s="53">
         <v>187</v>
       </c>
-      <c r="E30" s="52">
+      <c r="E30" s="51">
         <v>100</v>
       </c>
-      <c r="F30" s="50" t="s">
+      <c r="F30" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="G30" s="53">
+      <c r="G30" s="52">
         <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C31" s="51" t="s">
+      <c r="B31" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="54">
+      <c r="D31" s="53">
         <v>187</v>
       </c>
-      <c r="E31" s="52">
+      <c r="E31" s="51">
         <v>100</v>
       </c>
-      <c r="F31" s="50" t="s">
+      <c r="F31" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="G31" s="53">
+      <c r="G31" s="52">
         <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A32" s="50" t="s">
+      <c r="A32" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C32" s="51" t="s">
+      <c r="B32" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="D32" s="54">
+      <c r="D32" s="53">
         <v>187</v>
       </c>
-      <c r="E32" s="52">
+      <c r="E32" s="51">
         <v>100</v>
       </c>
-      <c r="F32" s="50" t="s">
+      <c r="F32" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="G32" s="53">
+      <c r="G32" s="52">
         <v>16</v>
       </c>
     </row>
@@ -3826,7 +3824,7 @@
       <c r="C33" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D33" s="45">
+      <c r="D33" s="44">
         <v>155</v>
       </c>
       <c r="E33" s="31">
@@ -3849,7 +3847,7 @@
       <c r="C34" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D34" s="45">
+      <c r="D34" s="44">
         <v>155</v>
       </c>
       <c r="E34" s="31">
@@ -3872,7 +3870,7 @@
       <c r="C35" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D35" s="45">
+      <c r="D35" s="44">
         <v>155</v>
       </c>
       <c r="E35" s="31">
@@ -3895,7 +3893,7 @@
       <c r="C36" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D36" s="45">
+      <c r="D36" s="44">
         <v>155</v>
       </c>
       <c r="E36" s="31">
@@ -3918,7 +3916,7 @@
       <c r="C37" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D37" s="45">
+      <c r="D37" s="44">
         <v>155</v>
       </c>
       <c r="E37" s="31">
@@ -3941,7 +3939,7 @@
       <c r="C38" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="45">
+      <c r="D38" s="44">
         <v>155</v>
       </c>
       <c r="E38" s="31">
@@ -3955,48 +3953,48 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A39" s="50" t="s">
+      <c r="A39" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="51" t="s">
+      <c r="B39" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D39" s="54">
+      <c r="D39" s="53">
         <v>155</v>
       </c>
-      <c r="E39" s="52">
+      <c r="E39" s="51">
         <v>25</v>
       </c>
-      <c r="F39" s="50" t="s">
+      <c r="F39" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="G39" s="53">
+      <c r="G39" s="52">
         <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A40" s="50" t="s">
+      <c r="A40" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="B40" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C40" s="51" t="s">
+      <c r="B40" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D40" s="54">
+      <c r="D40" s="53">
         <v>155</v>
       </c>
-      <c r="E40" s="52">
+      <c r="E40" s="51">
         <v>25</v>
       </c>
-      <c r="F40" s="50" t="s">
+      <c r="F40" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="G40" s="53">
+      <c r="G40" s="52">
         <v>20</v>
       </c>
     </row>
@@ -4010,7 +4008,7 @@
       <c r="C41" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D41" s="45">
+      <c r="D41" s="44">
         <v>180</v>
       </c>
       <c r="E41" s="31">
@@ -4033,7 +4031,7 @@
       <c r="C42" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D42" s="45">
+      <c r="D42" s="44">
         <v>180</v>
       </c>
       <c r="E42" s="31">
@@ -4056,7 +4054,7 @@
       <c r="C43" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="45">
+      <c r="D43" s="44">
         <v>180</v>
       </c>
       <c r="E43" s="31">
@@ -4079,7 +4077,7 @@
       <c r="C44" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D44" s="45">
+      <c r="D44" s="44">
         <v>180</v>
       </c>
       <c r="E44" s="31">
@@ -4102,7 +4100,7 @@
       <c r="C45" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D45" s="45">
+      <c r="D45" s="44">
         <v>180</v>
       </c>
       <c r="E45" s="31">
@@ -4125,7 +4123,7 @@
       <c r="C46" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D46" s="45">
+      <c r="D46" s="44">
         <v>180</v>
       </c>
       <c r="E46" s="31">
@@ -4139,71 +4137,71 @@
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A47" s="50" t="s">
+      <c r="A47" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="B47" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C47" s="51" t="s">
+      <c r="B47" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="D47" s="54">
+      <c r="D47" s="53">
         <v>180</v>
       </c>
-      <c r="E47" s="52">
+      <c r="E47" s="51">
         <v>50</v>
       </c>
-      <c r="F47" s="50" t="s">
+      <c r="F47" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="G47" s="53">
+      <c r="G47" s="52">
         <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A48" s="50" t="s">
+      <c r="A48" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="B48" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C48" s="51" t="s">
+      <c r="B48" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="D48" s="54">
+      <c r="D48" s="53">
         <v>180</v>
       </c>
-      <c r="E48" s="52">
+      <c r="E48" s="51">
         <v>50</v>
       </c>
-      <c r="F48" s="50" t="s">
+      <c r="F48" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="G48" s="53">
+      <c r="G48" s="52">
         <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A49" s="50" t="s">
+      <c r="A49" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C49" s="51" t="s">
+      <c r="B49" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C49" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="D49" s="54">
+      <c r="D49" s="53">
         <v>180</v>
       </c>
-      <c r="E49" s="52">
+      <c r="E49" s="51">
         <v>50</v>
       </c>
-      <c r="F49" s="50" t="s">
+      <c r="F49" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="G49" s="53">
+      <c r="G49" s="52">
         <v>16</v>
       </c>
     </row>
@@ -4217,7 +4215,7 @@
       <c r="C50" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D50" s="45">
+      <c r="D50" s="44">
         <v>200</v>
       </c>
       <c r="E50" s="31">
@@ -4240,7 +4238,7 @@
       <c r="C51" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D51" s="45">
+      <c r="D51" s="44">
         <v>200</v>
       </c>
       <c r="E51" s="31">
@@ -4263,7 +4261,7 @@
       <c r="C52" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D52" s="45">
+      <c r="D52" s="44">
         <v>200</v>
       </c>
       <c r="E52" s="31">
@@ -4286,7 +4284,7 @@
       <c r="C53" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D53" s="45">
+      <c r="D53" s="44">
         <v>200</v>
       </c>
       <c r="E53" s="31">
@@ -4309,7 +4307,7 @@
       <c r="C54" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D54" s="45">
+      <c r="D54" s="44">
         <v>200</v>
       </c>
       <c r="E54" s="31">
@@ -4323,48 +4321,48 @@
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A55" s="50" t="s">
+      <c r="A55" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="B55" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C55" s="51" t="s">
+      <c r="B55" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C55" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D55" s="54">
+      <c r="D55" s="53">
         <v>200</v>
       </c>
-      <c r="E55" s="52">
+      <c r="E55" s="51">
         <v>100</v>
       </c>
-      <c r="F55" s="50" t="s">
+      <c r="F55" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="G55" s="53">
+      <c r="G55" s="52">
         <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A56" s="50" t="s">
+      <c r="A56" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="B56" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C56" s="51" t="s">
+      <c r="B56" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C56" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D56" s="54">
+      <c r="D56" s="53">
         <v>200</v>
       </c>
-      <c r="E56" s="52">
+      <c r="E56" s="51">
         <v>100</v>
       </c>
-      <c r="F56" s="50" t="s">
+      <c r="F56" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="G56" s="53">
+      <c r="G56" s="52">
         <v>20</v>
       </c>
     </row>
@@ -4378,7 +4376,7 @@
       <c r="C57" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="D57" s="45">
+      <c r="D57" s="44">
         <v>187</v>
       </c>
       <c r="E57" s="31">
@@ -4401,7 +4399,7 @@
       <c r="C58" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="D58" s="45">
+      <c r="D58" s="44">
         <v>187</v>
       </c>
       <c r="E58" s="31">
@@ -4424,7 +4422,7 @@
       <c r="C59" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="D59" s="45">
+      <c r="D59" s="44">
         <v>187</v>
       </c>
       <c r="E59" s="31">
@@ -4447,7 +4445,7 @@
       <c r="C60" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="45">
+      <c r="D60" s="44">
         <v>187</v>
       </c>
       <c r="E60" s="31">
@@ -4461,71 +4459,71 @@
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A61" s="50" t="s">
+      <c r="A61" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="B61" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C61" s="51" t="s">
+      <c r="B61" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C61" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="D61" s="54">
+      <c r="D61" s="53">
         <v>187</v>
       </c>
-      <c r="E61" s="52">
+      <c r="E61" s="51">
         <v>100</v>
       </c>
-      <c r="F61" s="50" t="s">
+      <c r="F61" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="G61" s="53">
+      <c r="G61" s="52">
         <v>25</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A62" s="50" t="s">
+      <c r="A62" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="B62" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C62" s="51" t="s">
+      <c r="B62" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C62" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="D62" s="54">
+      <c r="D62" s="53">
         <v>187</v>
       </c>
-      <c r="E62" s="52">
+      <c r="E62" s="51">
         <v>100</v>
       </c>
-      <c r="F62" s="50" t="s">
+      <c r="F62" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="G62" s="53">
+      <c r="G62" s="52">
         <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A63" s="50" t="s">
+      <c r="A63" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="B63" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C63" s="51" t="s">
+      <c r="B63" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C63" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="D63" s="54">
+      <c r="D63" s="53">
         <v>187</v>
       </c>
-      <c r="E63" s="52">
+      <c r="E63" s="51">
         <v>100</v>
       </c>
-      <c r="F63" s="50" t="s">
+      <c r="F63" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="G63" s="53">
+      <c r="G63" s="52">
         <v>16</v>
       </c>
     </row>
@@ -4539,7 +4537,7 @@
       <c r="C64" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D64" s="45">
+      <c r="D64" s="44">
         <v>155</v>
       </c>
       <c r="E64" s="31">
@@ -4562,7 +4560,7 @@
       <c r="C65" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D65" s="45">
+      <c r="D65" s="44">
         <v>155</v>
       </c>
       <c r="E65" s="31">
@@ -4585,7 +4583,7 @@
       <c r="C66" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D66" s="45">
+      <c r="D66" s="44">
         <v>155</v>
       </c>
       <c r="E66" s="31">
@@ -4608,7 +4606,7 @@
       <c r="C67" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D67" s="45">
+      <c r="D67" s="44">
         <v>155</v>
       </c>
       <c r="E67" s="31">
@@ -4631,7 +4629,7 @@
       <c r="C68" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D68" s="45">
+      <c r="D68" s="44">
         <v>155</v>
       </c>
       <c r="E68" s="31">
@@ -4654,7 +4652,7 @@
       <c r="C69" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D69" s="45">
+      <c r="D69" s="44">
         <v>155</v>
       </c>
       <c r="E69" s="31">
@@ -4668,48 +4666,48 @@
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A70" s="50" t="s">
+      <c r="A70" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="B70" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C70" s="51" t="s">
+      <c r="B70" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C70" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D70" s="54">
+      <c r="D70" s="53">
         <v>155</v>
       </c>
-      <c r="E70" s="52">
+      <c r="E70" s="51">
         <v>25</v>
       </c>
-      <c r="F70" s="50" t="s">
+      <c r="F70" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="G70" s="53">
+      <c r="G70" s="52">
         <v>25</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A71" s="50" t="s">
+      <c r="A71" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="B71" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C71" s="51" t="s">
+      <c r="B71" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C71" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D71" s="54">
+      <c r="D71" s="53">
         <v>155</v>
       </c>
-      <c r="E71" s="52">
+      <c r="E71" s="51">
         <v>25</v>
       </c>
-      <c r="F71" s="50" t="s">
+      <c r="F71" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="G71" s="53">
+      <c r="G71" s="52">
         <v>20</v>
       </c>
     </row>
@@ -4723,7 +4721,7 @@
       <c r="C72" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D72" s="45">
+      <c r="D72" s="44">
         <v>180</v>
       </c>
       <c r="E72" s="31">
@@ -4746,7 +4744,7 @@
       <c r="C73" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D73" s="45">
+      <c r="D73" s="44">
         <v>180</v>
       </c>
       <c r="E73" s="31">
@@ -4769,7 +4767,7 @@
       <c r="C74" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D74" s="45">
+      <c r="D74" s="44">
         <v>180</v>
       </c>
       <c r="E74" s="31">
@@ -4792,7 +4790,7 @@
       <c r="C75" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D75" s="45">
+      <c r="D75" s="44">
         <v>180</v>
       </c>
       <c r="E75" s="31">
@@ -4815,7 +4813,7 @@
       <c r="C76" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D76" s="45">
+      <c r="D76" s="44">
         <v>180</v>
       </c>
       <c r="E76" s="31">
@@ -4838,7 +4836,7 @@
       <c r="C77" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D77" s="45">
+      <c r="D77" s="44">
         <v>180</v>
       </c>
       <c r="E77" s="31">
@@ -4852,71 +4850,71 @@
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A78" s="50" t="s">
+      <c r="A78" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="B78" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C78" s="51" t="s">
+      <c r="B78" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C78" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="D78" s="54">
+      <c r="D78" s="53">
         <v>180</v>
       </c>
-      <c r="E78" s="52">
+      <c r="E78" s="51">
         <v>50</v>
       </c>
-      <c r="F78" s="50" t="s">
+      <c r="F78" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="G78" s="53">
+      <c r="G78" s="52">
         <v>25</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A79" s="50" t="s">
+      <c r="A79" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="B79" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C79" s="51" t="s">
+      <c r="B79" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C79" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="D79" s="54">
+      <c r="D79" s="53">
         <v>180</v>
       </c>
-      <c r="E79" s="52">
+      <c r="E79" s="51">
         <v>50</v>
       </c>
-      <c r="F79" s="50" t="s">
+      <c r="F79" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="G79" s="53">
+      <c r="G79" s="52">
         <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A80" s="50" t="s">
+      <c r="A80" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="B80" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C80" s="51" t="s">
+      <c r="B80" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C80" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="D80" s="54">
+      <c r="D80" s="53">
         <v>180</v>
       </c>
-      <c r="E80" s="52">
+      <c r="E80" s="51">
         <v>50</v>
       </c>
-      <c r="F80" s="50" t="s">
+      <c r="F80" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="G80" s="53">
+      <c r="G80" s="52">
         <v>16</v>
       </c>
     </row>
@@ -4930,7 +4928,7 @@
       <c r="C81" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D81" s="45">
+      <c r="D81" s="44">
         <v>200</v>
       </c>
       <c r="E81" s="31">
@@ -4953,7 +4951,7 @@
       <c r="C82" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D82" s="45">
+      <c r="D82" s="44">
         <v>200</v>
       </c>
       <c r="E82" s="31">
@@ -4976,7 +4974,7 @@
       <c r="C83" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D83" s="45">
+      <c r="D83" s="44">
         <v>200</v>
       </c>
       <c r="E83" s="31">
@@ -4999,7 +4997,7 @@
       <c r="C84" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D84" s="45">
+      <c r="D84" s="44">
         <v>200</v>
       </c>
       <c r="E84" s="31">
@@ -5022,7 +5020,7 @@
       <c r="C85" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D85" s="45">
+      <c r="D85" s="44">
         <v>200</v>
       </c>
       <c r="E85" s="31">
@@ -5036,48 +5034,48 @@
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A86" s="50" t="s">
+      <c r="A86" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="B86" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C86" s="51" t="s">
+      <c r="B86" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C86" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D86" s="54">
+      <c r="D86" s="53">
         <v>200</v>
       </c>
-      <c r="E86" s="52">
+      <c r="E86" s="51">
         <v>100</v>
       </c>
-      <c r="F86" s="50" t="s">
+      <c r="F86" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="G86" s="53">
+      <c r="G86" s="52">
         <v>25</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A87" s="50" t="s">
+      <c r="A87" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="B87" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C87" s="51" t="s">
+      <c r="B87" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C87" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D87" s="54">
+      <c r="D87" s="53">
         <v>200</v>
       </c>
-      <c r="E87" s="52">
+      <c r="E87" s="51">
         <v>100</v>
       </c>
-      <c r="F87" s="50" t="s">
+      <c r="F87" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="G87" s="53">
+      <c r="G87" s="52">
         <v>20</v>
       </c>
     </row>
@@ -5091,7 +5089,7 @@
       <c r="C88" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="D88" s="45">
+      <c r="D88" s="44">
         <v>187</v>
       </c>
       <c r="E88" s="31">
@@ -5114,7 +5112,7 @@
       <c r="C89" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="D89" s="45">
+      <c r="D89" s="44">
         <v>187</v>
       </c>
       <c r="E89" s="31">
@@ -5137,7 +5135,7 @@
       <c r="C90" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="D90" s="45">
+      <c r="D90" s="44">
         <v>187</v>
       </c>
       <c r="E90" s="31">
@@ -5160,7 +5158,7 @@
       <c r="C91" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="D91" s="45">
+      <c r="D91" s="44">
         <v>187</v>
       </c>
       <c r="E91" s="31">
@@ -5174,71 +5172,71 @@
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A92" s="50" t="s">
+      <c r="A92" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="B92" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C92" s="51" t="s">
+      <c r="B92" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C92" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="D92" s="54">
+      <c r="D92" s="53">
         <v>187</v>
       </c>
-      <c r="E92" s="52">
+      <c r="E92" s="51">
         <v>100</v>
       </c>
-      <c r="F92" s="50" t="s">
+      <c r="F92" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="G92" s="53">
+      <c r="G92" s="52">
         <v>25</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A93" s="50" t="s">
+      <c r="A93" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="B93" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C93" s="51" t="s">
+      <c r="B93" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C93" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="D93" s="54">
+      <c r="D93" s="53">
         <v>187</v>
       </c>
-      <c r="E93" s="52">
+      <c r="E93" s="51">
         <v>100</v>
       </c>
-      <c r="F93" s="50" t="s">
+      <c r="F93" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="G93" s="53">
+      <c r="G93" s="52">
         <v>20</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A94" s="50" t="s">
+      <c r="A94" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="B94" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C94" s="51" t="s">
+      <c r="B94" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C94" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="D94" s="54">
+      <c r="D94" s="53">
         <v>187</v>
       </c>
-      <c r="E94" s="52">
+      <c r="E94" s="51">
         <v>100</v>
       </c>
-      <c r="F94" s="50" t="s">
+      <c r="F94" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="G94" s="53">
+      <c r="G94" s="52">
         <v>16</v>
       </c>
     </row>
@@ -5256,525 +5254,534 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="19.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="11.44140625" style="1"/>
+    <col min="1" max="1" width="23.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="39" x14ac:dyDescent="0.45">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="56" t="s">
+      <c r="C1" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="56" t="s">
+      <c r="D1" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="57" t="s">
+      <c r="F1" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="58" t="s">
+      <c r="G1" s="57" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="31">
+      <c r="D2" s="59">
         <v>86</v>
       </c>
-      <c r="E2" s="34">
+      <c r="E2" s="51">
         <v>86</v>
       </c>
-      <c r="F2" s="35"/>
-      <c r="G2" s="36"/>
+      <c r="F2" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="60">
+        <v>20</v>
+      </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="59">
+        <v>86</v>
+      </c>
+      <c r="E3" s="52">
+        <v>86</v>
+      </c>
+      <c r="F3" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="52">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B4" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C4" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="31">
+      <c r="D4" s="59">
         <v>86</v>
       </c>
-      <c r="E3" s="34">
+      <c r="E4" s="59">
         <v>86</v>
       </c>
-      <c r="F3" s="35"/>
-      <c r="G3" s="36"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="33" t="s">
+      <c r="F4" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="60">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="59">
+        <v>86</v>
+      </c>
+      <c r="E5" s="59">
+        <v>86</v>
+      </c>
+      <c r="F5" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="52">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B6" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C6" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D6" s="31">
         <v>150</v>
       </c>
-      <c r="E4" s="34">
+      <c r="E6" s="34">
         <v>100</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F6" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="38">
+      <c r="G6" s="37">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="33" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B7" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C7" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D7" s="31">
         <v>150</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E7" s="34">
         <v>100</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F7" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="38">
+      <c r="G7" s="37">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="59" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B8" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C8" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="52">
+      <c r="D8" s="51">
         <v>150</v>
       </c>
-      <c r="E6" s="60">
+      <c r="E8" s="59">
         <v>100</v>
       </c>
-      <c r="F6" s="51" t="s">
+      <c r="F8" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="61">
+      <c r="G8" s="60">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" s="59" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B9" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C9" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D9" s="51">
         <v>150</v>
       </c>
-      <c r="E7" s="60">
+      <c r="E9" s="59">
         <v>100</v>
       </c>
-      <c r="F7" s="51" t="s">
+      <c r="F9" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="61">
+      <c r="G9" s="60">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" s="59" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="B10" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="51" t="s">
+      <c r="C10" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="52">
+      <c r="D10" s="51">
         <v>150</v>
       </c>
-      <c r="E8" s="60">
+      <c r="E10" s="59">
         <v>100</v>
       </c>
-      <c r="F8" s="51" t="s">
+      <c r="F10" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="61">
+      <c r="G10" s="60">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="59" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B11" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="C11" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="52">
+      <c r="D11" s="51">
         <v>150</v>
       </c>
-      <c r="E9" s="60">
+      <c r="E11" s="59">
         <v>100</v>
       </c>
-      <c r="F9" s="51" t="s">
+      <c r="F11" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="61">
+      <c r="G11" s="60">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="59" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A12" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="51" t="s">
+      <c r="B12" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C12" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="52">
+      <c r="D12" s="51">
         <v>150</v>
       </c>
-      <c r="E10" s="60">
+      <c r="E12" s="59">
         <v>100</v>
       </c>
-      <c r="F10" s="51" t="s">
+      <c r="F12" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="61">
+      <c r="G12" s="60">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" s="33" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B13" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C13" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D13" s="31">
         <v>150</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E13" s="34">
         <v>100</v>
       </c>
-      <c r="F11" s="30" t="s">
+      <c r="F13" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G13" s="37">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A12" s="33" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A14" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B14" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C14" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D14" s="31">
         <v>150</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E14" s="34">
         <v>100</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="F14" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="38">
+      <c r="G14" s="37">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="59" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A15" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B15" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="51" t="s">
+      <c r="C15" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="52">
+      <c r="D15" s="51">
         <v>150</v>
       </c>
-      <c r="E13" s="60">
+      <c r="E15" s="59">
         <v>100</v>
       </c>
-      <c r="F13" s="51" t="s">
+      <c r="F15" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="G13" s="61">
+      <c r="G15" s="60">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A14" s="59" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A16" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="51" t="s">
+      <c r="B16" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C16" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="52">
+      <c r="D16" s="51">
         <v>150</v>
       </c>
-      <c r="E14" s="60">
+      <c r="E16" s="59">
         <v>100</v>
       </c>
-      <c r="F14" s="51" t="s">
+      <c r="F16" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="61">
+      <c r="G16" s="60">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A15" s="59" t="s">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A17" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="51" t="s">
+      <c r="B17" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="51" t="s">
+      <c r="C17" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="52">
+      <c r="D17" s="51">
         <v>150</v>
       </c>
-      <c r="E15" s="60">
+      <c r="E17" s="59">
         <v>100</v>
       </c>
-      <c r="F15" s="51" t="s">
+      <c r="F17" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="61">
+      <c r="G17" s="60">
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A16" s="59" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A18" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B18" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="51" t="s">
+      <c r="C18" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="52">
+      <c r="D18" s="51">
         <v>150</v>
       </c>
-      <c r="E16" s="60">
+      <c r="E18" s="59">
         <v>100</v>
       </c>
-      <c r="F16" s="51" t="s">
+      <c r="F18" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="61">
+      <c r="G18" s="60">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" s="59" t="s">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A19" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="51" t="s">
+      <c r="B19" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="51" t="s">
+      <c r="C19" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="52">
+      <c r="D19" s="51">
         <v>150</v>
       </c>
-      <c r="E17" s="60">
+      <c r="E19" s="59">
         <v>100</v>
       </c>
-      <c r="F17" s="51" t="s">
+      <c r="F19" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="G17" s="61">
+      <c r="G19" s="60">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A18" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="31">
-        <v>170</v>
-      </c>
-      <c r="E18" s="34">
-        <v>170</v>
-      </c>
-      <c r="F18" s="29"/>
-      <c r="G18" s="38"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="31">
-        <v>170</v>
-      </c>
-      <c r="E19" s="34">
-        <v>170</v>
-      </c>
-      <c r="F19" s="29"/>
-      <c r="G19" s="38"/>
-    </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A20" s="37" t="s">
+      <c r="A20" s="36" t="s">
         <v>33</v>
       </c>
       <c r="B20" s="30" t="s">
         <v>39</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D20" s="31">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="E20" s="34">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="F20" s="29"/>
-      <c r="G20" s="38"/>
+      <c r="G20" s="37"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="36" t="s">
         <v>40</v>
       </c>
       <c r="B21" s="30" t="s">
         <v>39</v>
       </c>
       <c r="C21" s="30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D21" s="31">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="E21" s="34">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="F21" s="29"/>
-      <c r="G21" s="38"/>
+      <c r="G21" s="37"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A22" s="37" t="s">
-        <v>34</v>
+      <c r="A22" s="36" t="s">
+        <v>33</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="34">
-        <v>330</v>
-      </c>
-      <c r="E22" s="31">
+      <c r="C22" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="31">
         <v>140</v>
       </c>
-      <c r="F22" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="G22" s="38">
-        <v>13</v>
-      </c>
+      <c r="E22" s="34">
+        <v>140</v>
+      </c>
+      <c r="F22" s="29"/>
+      <c r="G22" s="37"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A23" s="37" t="s">
-        <v>34</v>
+      <c r="A23" s="36" t="s">
+        <v>40</v>
       </c>
       <c r="B23" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="34">
-        <v>330</v>
-      </c>
-      <c r="E23" s="31">
+      <c r="C23" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="31">
         <v>140</v>
       </c>
-      <c r="F23" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G23" s="38">
-        <v>20</v>
-      </c>
+      <c r="E23" s="34">
+        <v>140</v>
+      </c>
+      <c r="F23" s="29"/>
+      <c r="G23" s="37"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="36" t="s">
         <v>34</v>
       </c>
       <c r="B24" s="30" t="s">
@@ -5790,14 +5797,14 @@
         <v>140</v>
       </c>
       <c r="F24" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="38">
-        <v>30</v>
+        <v>2</v>
+      </c>
+      <c r="G24" s="37">
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="36" t="s">
         <v>34</v>
       </c>
       <c r="B25" s="30" t="s">
@@ -5813,14 +5820,14 @@
         <v>140</v>
       </c>
       <c r="F25" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G25" s="38">
-        <v>17</v>
+        <v>3</v>
+      </c>
+      <c r="G25" s="37">
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="36" t="s">
         <v>34</v>
       </c>
       <c r="B26" s="30" t="s">
@@ -5836,14 +5843,14 @@
         <v>140</v>
       </c>
       <c r="F26" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="G26" s="38">
-        <v>20</v>
+        <v>5</v>
+      </c>
+      <c r="G26" s="37">
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="36" t="s">
         <v>34</v>
       </c>
       <c r="B27" s="30" t="s">
@@ -5859,129 +5866,129 @@
         <v>140</v>
       </c>
       <c r="F27" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27" s="37">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A28" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="34">
+        <v>330</v>
+      </c>
+      <c r="E28" s="31">
+        <v>140</v>
+      </c>
+      <c r="F28" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28" s="37">
         <v>20</v>
       </c>
-      <c r="G27" s="38">
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A29" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="34">
+        <v>330</v>
+      </c>
+      <c r="E29" s="31">
+        <v>140</v>
+      </c>
+      <c r="F29" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="37">
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A28" s="62" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A30" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="51" t="s">
+      <c r="B30" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="63" t="s">
+      <c r="C30" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D28" s="60">
+      <c r="D30" s="59">
         <v>330</v>
       </c>
-      <c r="E28" s="52">
+      <c r="E30" s="51">
         <v>140</v>
       </c>
-      <c r="F28" s="50" t="s">
+      <c r="F30" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="G28" s="53">
+      <c r="G30" s="52">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A29" s="62" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A31" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="51" t="s">
+      <c r="B31" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="63" t="s">
+      <c r="C31" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="60">
+      <c r="D31" s="59">
         <v>330</v>
       </c>
-      <c r="E29" s="52">
+      <c r="E31" s="51">
         <v>140</v>
       </c>
-      <c r="F29" s="50" t="s">
+      <c r="F31" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="G29" s="53">
+      <c r="G31" s="52">
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A30" s="62" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A32" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="51" t="s">
+      <c r="B32" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="63" t="s">
+      <c r="C32" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="60">
+      <c r="D32" s="59">
         <v>330</v>
       </c>
-      <c r="E30" s="52">
+      <c r="E32" s="51">
         <v>140</v>
       </c>
-      <c r="F30" s="50" t="s">
+      <c r="F32" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="G30" s="53">
+      <c r="G32" s="52">
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A31" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="34">
-        <v>330</v>
-      </c>
-      <c r="E31" s="31">
-        <v>140</v>
-      </c>
-      <c r="F31" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="G31" s="38">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A32" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="34">
-        <v>330</v>
-      </c>
-      <c r="E32" s="31">
-        <v>140</v>
-      </c>
-      <c r="F32" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="38">
-        <v>20</v>
-      </c>
-    </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A33" s="37" t="s">
+      <c r="A33" s="36" t="s">
         <v>40</v>
       </c>
       <c r="B33" s="30" t="s">
@@ -5997,14 +6004,14 @@
         <v>140</v>
       </c>
       <c r="F33" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" s="38">
-        <v>30</v>
+        <v>2</v>
+      </c>
+      <c r="G33" s="37">
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A34" s="37" t="s">
+      <c r="A34" s="36" t="s">
         <v>40</v>
       </c>
       <c r="B34" s="30" t="s">
@@ -6020,14 +6027,14 @@
         <v>140</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G34" s="38">
-        <v>17</v>
+        <v>3</v>
+      </c>
+      <c r="G34" s="37">
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A35" s="37" t="s">
+      <c r="A35" s="36" t="s">
         <v>40</v>
       </c>
       <c r="B35" s="30" t="s">
@@ -6043,14 +6050,14 @@
         <v>140</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="G35" s="38">
-        <v>20</v>
+        <v>5</v>
+      </c>
+      <c r="G35" s="37">
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A36" s="37" t="s">
+      <c r="A36" s="36" t="s">
         <v>40</v>
       </c>
       <c r="B36" s="30" t="s">
@@ -6066,129 +6073,129 @@
         <v>140</v>
       </c>
       <c r="F36" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G36" s="37">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A37" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="34">
+        <v>330</v>
+      </c>
+      <c r="E37" s="31">
+        <v>140</v>
+      </c>
+      <c r="F37" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="G37" s="37">
         <v>20</v>
       </c>
-      <c r="G36" s="38">
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A38" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="34">
+        <v>330</v>
+      </c>
+      <c r="E38" s="31">
+        <v>140</v>
+      </c>
+      <c r="F38" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="37">
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A37" s="62" t="s">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A39" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="51" t="s">
+      <c r="B39" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="63" t="s">
+      <c r="C39" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D37" s="60">
+      <c r="D39" s="59">
         <v>330</v>
       </c>
-      <c r="E37" s="52">
+      <c r="E39" s="51">
         <v>140</v>
       </c>
-      <c r="F37" s="50" t="s">
+      <c r="F39" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="G37" s="53">
+      <c r="G39" s="52">
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A38" s="62" t="s">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A40" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="51" t="s">
+      <c r="B40" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="63" t="s">
+      <c r="C40" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="60">
+      <c r="D40" s="59">
         <v>330</v>
       </c>
-      <c r="E38" s="52">
+      <c r="E40" s="51">
         <v>140</v>
       </c>
-      <c r="F38" s="50" t="s">
+      <c r="F40" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="G38" s="53">
+      <c r="G40" s="52">
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A39" s="62" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A41" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="51" t="s">
+      <c r="B41" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="63" t="s">
+      <c r="C41" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D39" s="60">
+      <c r="D41" s="59">
         <v>330</v>
       </c>
-      <c r="E39" s="52">
+      <c r="E41" s="51">
         <v>140</v>
       </c>
-      <c r="F39" s="50" t="s">
+      <c r="F41" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="G39" s="53">
+      <c r="G41" s="52">
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A40" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="B40" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="C40" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="32">
-        <v>330</v>
-      </c>
-      <c r="E40" s="31">
-        <v>140</v>
-      </c>
-      <c r="F40" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="G40" s="38">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A41" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="B41" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="C41" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="32">
-        <v>330</v>
-      </c>
-      <c r="E41" s="31">
-        <v>140</v>
-      </c>
-      <c r="F41" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" s="38">
-        <v>20</v>
-      </c>
-    </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A42" s="37" t="s">
+      <c r="A42" s="36" t="s">
         <v>33</v>
       </c>
       <c r="B42" s="30" t="s">
@@ -6204,14 +6211,14 @@
         <v>140</v>
       </c>
       <c r="F42" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="G42" s="38">
-        <v>30</v>
+        <v>2</v>
+      </c>
+      <c r="G42" s="37">
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A43" s="37" t="s">
+      <c r="A43" s="36" t="s">
         <v>33</v>
       </c>
       <c r="B43" s="30" t="s">
@@ -6227,14 +6234,14 @@
         <v>140</v>
       </c>
       <c r="F43" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G43" s="38">
-        <v>17</v>
+        <v>3</v>
+      </c>
+      <c r="G43" s="37">
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A44" s="37" t="s">
+      <c r="A44" s="36" t="s">
         <v>33</v>
       </c>
       <c r="B44" s="30" t="s">
@@ -6250,101 +6257,147 @@
         <v>140</v>
       </c>
       <c r="F44" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="G44" s="38">
-        <v>20</v>
+        <v>5</v>
+      </c>
+      <c r="G44" s="37">
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A45" s="37" t="s">
+      <c r="A45" s="36" t="s">
         <v>33</v>
       </c>
       <c r="B45" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C45" s="46" t="s">
+      <c r="C45" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="D45" s="47">
+      <c r="D45" s="32">
         <v>330</v>
       </c>
-      <c r="E45" s="64">
+      <c r="E45" s="31">
         <v>140</v>
       </c>
-      <c r="F45" s="46" t="s">
+      <c r="F45" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G45" s="37">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A46" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B46" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="32">
+        <v>330</v>
+      </c>
+      <c r="E46" s="31">
+        <v>140</v>
+      </c>
+      <c r="F46" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="G46" s="37">
         <v>20</v>
       </c>
-      <c r="G45" s="65">
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A47" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B47" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="46">
+        <v>330</v>
+      </c>
+      <c r="E47" s="63">
+        <v>140</v>
+      </c>
+      <c r="F47" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" s="64">
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A46" s="62" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A48" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="51" t="s">
+      <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="66" t="s">
+      <c r="C48" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="D46" s="72">
+      <c r="D48" s="71">
         <v>330</v>
       </c>
-      <c r="E46" s="67">
+      <c r="E48" s="66">
         <v>140</v>
       </c>
-      <c r="F46" s="68" t="s">
+      <c r="F48" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="G46" s="69">
+      <c r="G48" s="68">
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A47" s="62" t="s">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A49" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="B47" s="51" t="s">
+      <c r="B49" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="66" t="s">
+      <c r="C49" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="D47" s="72">
+      <c r="D49" s="71">
         <v>330</v>
       </c>
-      <c r="E47" s="67">
+      <c r="E49" s="66">
         <v>140</v>
       </c>
-      <c r="F47" s="68" t="s">
+      <c r="F49" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="G47" s="69">
+      <c r="G49" s="68">
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A48" s="62" t="s">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A50" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="B48" s="51" t="s">
+      <c r="B50" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="66" t="s">
+      <c r="C50" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="D48" s="72">
+      <c r="D50" s="71">
         <v>330</v>
       </c>
-      <c r="E48" s="67">
+      <c r="E50" s="66">
         <v>140</v>
       </c>
-      <c r="F48" s="70" t="s">
+      <c r="F50" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="G48" s="71">
+      <c r="G50" s="70">
         <v>16</v>
       </c>
     </row>
@@ -6445,7 +6498,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B4" s="10" t="s">
@@ -6460,7 +6513,7 @@
       <c r="E4" s="13">
         <v>270</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="42" t="s">
         <v>42</v>
       </c>
       <c r="G4" s="13">
@@ -6468,7 +6521,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B5" s="10" t="s">
@@ -6483,7 +6536,7 @@
       <c r="E5" s="13">
         <v>270</v>
       </c>
-      <c r="F5" s="43" t="s">
+      <c r="F5" s="42" t="s">
         <v>25</v>
       </c>
       <c r="G5" s="13">
@@ -6629,7 +6682,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="10" t="s">
@@ -6644,7 +6697,7 @@
       <c r="E12" s="13">
         <v>50</v>
       </c>
-      <c r="F12" s="44" t="s">
+      <c r="F12" s="43" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="19">
@@ -6652,7 +6705,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="10" t="s">
@@ -6667,7 +6720,7 @@
       <c r="E13" s="13">
         <v>50</v>
       </c>
-      <c r="F13" s="44" t="s">
+      <c r="F13" s="43" t="s">
         <v>42</v>
       </c>
       <c r="G13" s="19">
@@ -6675,7 +6728,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A14" s="43" t="s">
+      <c r="A14" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B14" s="10" t="s">
@@ -6690,7 +6743,7 @@
       <c r="E14" s="13">
         <v>50</v>
       </c>
-      <c r="F14" s="44" t="s">
+      <c r="F14" s="43" t="s">
         <v>25</v>
       </c>
       <c r="G14" s="19">
@@ -6813,7 +6866,7 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A20" s="43" t="s">
+      <c r="A20" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B20" s="10" t="s">
@@ -6828,7 +6881,7 @@
       <c r="E20" s="13">
         <v>100</v>
       </c>
-      <c r="F20" s="44" t="s">
+      <c r="F20" s="43" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="19">
@@ -6836,7 +6889,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" s="43" t="s">
+      <c r="A21" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B21" s="10" t="s">
@@ -6851,7 +6904,7 @@
       <c r="E21" s="13">
         <v>100</v>
       </c>
-      <c r="F21" s="44" t="s">
+      <c r="F21" s="43" t="s">
         <v>42</v>
       </c>
       <c r="G21" s="19">
@@ -6859,7 +6912,7 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="10" t="s">
@@ -6874,7 +6927,7 @@
       <c r="E22" s="13">
         <v>100</v>
       </c>
-      <c r="F22" s="44" t="s">
+      <c r="F22" s="43" t="s">
         <v>25</v>
       </c>
       <c r="G22" s="19">
@@ -6974,7 +7027,7 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A27" s="43" t="s">
+      <c r="A27" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B27" s="10" t="s">
@@ -6989,7 +7042,7 @@
       <c r="E27" s="13">
         <v>75</v>
       </c>
-      <c r="F27" s="44" t="s">
+      <c r="F27" s="43" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="19">
@@ -6997,7 +7050,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A28" s="43" t="s">
+      <c r="A28" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B28" s="10" t="s">
@@ -7012,7 +7065,7 @@
       <c r="E28" s="13">
         <v>75</v>
       </c>
-      <c r="F28" s="44" t="s">
+      <c r="F28" s="43" t="s">
         <v>42</v>
       </c>
       <c r="G28" s="19">
@@ -7020,7 +7073,7 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A29" s="43" t="s">
+      <c r="A29" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B29" s="10" t="s">
@@ -7035,7 +7088,7 @@
       <c r="E29" s="13">
         <v>75</v>
       </c>
-      <c r="F29" s="44" t="s">
+      <c r="F29" s="43" t="s">
         <v>25</v>
       </c>
       <c r="G29" s="19">
@@ -7089,7 +7142,7 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A32" s="43" t="s">
+      <c r="A32" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B32" s="10" t="s">
@@ -7104,7 +7157,7 @@
       <c r="E32" s="13">
         <v>270</v>
       </c>
-      <c r="F32" s="43" t="s">
+      <c r="F32" s="42" t="s">
         <v>42</v>
       </c>
       <c r="G32" s="13">
@@ -7112,7 +7165,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A33" s="43" t="s">
+      <c r="A33" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B33" s="10" t="s">
@@ -7127,7 +7180,7 @@
       <c r="E33" s="13">
         <v>270</v>
       </c>
-      <c r="F33" s="43" t="s">
+      <c r="F33" s="42" t="s">
         <v>25</v>
       </c>
       <c r="G33" s="13">
@@ -7273,7 +7326,7 @@
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A40" s="44" t="s">
+      <c r="A40" s="43" t="s">
         <v>40</v>
       </c>
       <c r="B40" s="14" t="s">
@@ -7288,7 +7341,7 @@
       <c r="E40" s="19">
         <v>50</v>
       </c>
-      <c r="F40" s="44" t="s">
+      <c r="F40" s="43" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="19">
@@ -7296,7 +7349,7 @@
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A41" s="44" t="s">
+      <c r="A41" s="43" t="s">
         <v>40</v>
       </c>
       <c r="B41" s="14" t="s">
@@ -7311,7 +7364,7 @@
       <c r="E41" s="19">
         <v>50</v>
       </c>
-      <c r="F41" s="44" t="s">
+      <c r="F41" s="43" t="s">
         <v>42</v>
       </c>
       <c r="G41" s="19">
@@ -7319,7 +7372,7 @@
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A42" s="44" t="s">
+      <c r="A42" s="43" t="s">
         <v>40</v>
       </c>
       <c r="B42" s="14" t="s">
@@ -7334,7 +7387,7 @@
       <c r="E42" s="19">
         <v>50</v>
       </c>
-      <c r="F42" s="44" t="s">
+      <c r="F42" s="43" t="s">
         <v>25</v>
       </c>
       <c r="G42" s="19">
@@ -7457,7 +7510,7 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A48" s="43" t="s">
+      <c r="A48" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B48" s="10" t="s">
@@ -7472,7 +7525,7 @@
       <c r="E48" s="13">
         <v>100</v>
       </c>
-      <c r="F48" s="44" t="s">
+      <c r="F48" s="43" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="19">
@@ -7480,7 +7533,7 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A49" s="43" t="s">
+      <c r="A49" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B49" s="10" t="s">
@@ -7495,7 +7548,7 @@
       <c r="E49" s="13">
         <v>100</v>
       </c>
-      <c r="F49" s="44" t="s">
+      <c r="F49" s="43" t="s">
         <v>42</v>
       </c>
       <c r="G49" s="19">
@@ -7503,7 +7556,7 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A50" s="43" t="s">
+      <c r="A50" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B50" s="10" t="s">
@@ -7518,7 +7571,7 @@
       <c r="E50" s="13">
         <v>100</v>
       </c>
-      <c r="F50" s="44" t="s">
+      <c r="F50" s="43" t="s">
         <v>25</v>
       </c>
       <c r="G50" s="19">
@@ -7618,7 +7671,7 @@
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A55" s="43" t="s">
+      <c r="A55" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B55" s="10" t="s">
@@ -7633,7 +7686,7 @@
       <c r="E55" s="13">
         <v>75</v>
       </c>
-      <c r="F55" s="44" t="s">
+      <c r="F55" s="43" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="19">
@@ -7641,7 +7694,7 @@
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A56" s="43" t="s">
+      <c r="A56" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B56" s="10" t="s">
@@ -7656,7 +7709,7 @@
       <c r="E56" s="13">
         <v>75</v>
       </c>
-      <c r="F56" s="44" t="s">
+      <c r="F56" s="43" t="s">
         <v>42</v>
       </c>
       <c r="G56" s="19">
@@ -7664,7 +7717,7 @@
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A57" s="43" t="s">
+      <c r="A57" s="42" t="s">
         <v>33</v>
       </c>
       <c r="B57" s="10" t="s">
@@ -7679,7 +7732,7 @@
       <c r="E57" s="13">
         <v>75</v>
       </c>
-      <c r="F57" s="44" t="s">
+      <c r="F57" s="43" t="s">
         <v>25</v>
       </c>
       <c r="G57" s="19">
@@ -7722,7 +7775,7 @@
       <c r="C1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="40" t="s">
         <v>41</v>
       </c>
       <c r="E1" s="7" t="s">
@@ -7742,10 +7795,10 @@
       <c r="B2" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="42">
+      <c r="D2" s="41">
         <v>25</v>
       </c>
       <c r="E2" s="4">
@@ -7813,7 +7866,7 @@
       <c r="C2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="39">
+      <c r="D2" s="38">
         <v>14</v>
       </c>
       <c r="E2" s="13">
@@ -7836,7 +7889,7 @@
       <c r="C3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="40">
+      <c r="D3" s="39">
         <v>14</v>
       </c>
       <c r="E3" s="28">

--- a/catalogos/CATALOGO_LINEAS_VALIDAS_21082026.xlsx
+++ b/catalogos/CATALOGO_LINEAS_VALIDAS_21082026.xlsx
@@ -204,6 +204,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Noto Sans"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -564,121 +565,6 @@
   </cellStyles>
   <dxfs count="62">
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
       <border outline="0">
         <left style="thin">
@@ -1628,6 +1514,121 @@
         <name val="Noto Sans"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill patternType="none">
@@ -2468,59 +2469,71 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Tabla1" displayName="Tabla1" ref="A1:G50" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41" tableBorderDxfId="39" totalsRowBorderDxfId="38">
+  <autoFilter ref="A1:G50">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Subsidio 100% CONAVI"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Adquisición de vivienda nueva"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="7">
     <tableColumn id="1" name="esquema" dataDxfId="37"/>
     <tableColumn id="2" name="modalidad" dataDxfId="36"/>
     <tableColumn id="3" name="linea_de_apoyo" dataDxfId="35"/>
-    <tableColumn id="7" name="uma_max" dataDxfId="2"/>
-    <tableColumn id="4" name="uma_la" dataDxfId="0"/>
-    <tableColumn id="5" name="linea_complementaria" dataDxfId="1"/>
-    <tableColumn id="6" name="uma_lc" dataDxfId="34"/>
+    <tableColumn id="7" name="uma_max" dataDxfId="34"/>
+    <tableColumn id="4" name="uma_la" dataDxfId="33"/>
+    <tableColumn id="5" name="linea_complementaria" dataDxfId="32"/>
+    <tableColumn id="6" name="uma_lc" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabla2" displayName="Tabla2" ref="A1:G57" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabla2" displayName="Tabla2" ref="A1:G57" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <tableColumns count="7">
-    <tableColumn id="1" name="esquema" dataDxfId="31"/>
-    <tableColumn id="2" name="modalidad" dataDxfId="30"/>
-    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="29"/>
-    <tableColumn id="8" name="uma_max" dataDxfId="28"/>
-    <tableColumn id="4" name="uma_la" dataDxfId="27"/>
-    <tableColumn id="5" name="linea_complementaria" dataDxfId="26"/>
-    <tableColumn id="6" name="uma_lc" dataDxfId="25"/>
+    <tableColumn id="1" name="esquema" dataDxfId="28"/>
+    <tableColumn id="2" name="modalidad" dataDxfId="27"/>
+    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="26"/>
+    <tableColumn id="8" name="uma_max" dataDxfId="25"/>
+    <tableColumn id="4" name="uma_la" dataDxfId="24"/>
+    <tableColumn id="5" name="linea_complementaria" dataDxfId="23"/>
+    <tableColumn id="6" name="uma_lc" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tabla5" displayName="Tabla5" ref="A1:G2" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23" tableBorderDxfId="22" totalsRowBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tabla5" displayName="Tabla5" ref="A1:G2" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <tableColumns count="7">
-    <tableColumn id="1" name="esquema" dataDxfId="20"/>
-    <tableColumn id="2" name="modalidad" dataDxfId="19"/>
-    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="18"/>
-    <tableColumn id="7" name="uma_max" dataDxfId="17"/>
-    <tableColumn id="4" name="uma_la" dataDxfId="16"/>
-    <tableColumn id="5" name="linea_complementaria" dataDxfId="15"/>
-    <tableColumn id="6" name="uma_lc" dataDxfId="14"/>
+    <tableColumn id="1" name="esquema" dataDxfId="17"/>
+    <tableColumn id="2" name="modalidad" dataDxfId="16"/>
+    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="15"/>
+    <tableColumn id="7" name="uma_max" dataDxfId="14"/>
+    <tableColumn id="4" name="uma_la" dataDxfId="13"/>
+    <tableColumn id="5" name="linea_complementaria" dataDxfId="12"/>
+    <tableColumn id="6" name="uma_lc" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Tabla6" displayName="Tabla6" ref="A1:G3" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Tabla6" displayName="Tabla6" ref="A1:G3" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <tableColumns count="7">
-    <tableColumn id="1" name="esquema" dataDxfId="9"/>
-    <tableColumn id="2" name="modalidad" dataDxfId="8"/>
-    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="7"/>
-    <tableColumn id="7" name="uma_max" dataDxfId="6"/>
-    <tableColumn id="4" name="uma_la" dataDxfId="5"/>
-    <tableColumn id="5" name="linea_complementaria" dataDxfId="4"/>
-    <tableColumn id="6" name="uma_lc" dataDxfId="3"/>
+    <tableColumn id="1" name="esquema" dataDxfId="6"/>
+    <tableColumn id="2" name="modalidad" dataDxfId="5"/>
+    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="4"/>
+    <tableColumn id="7" name="uma_max" dataDxfId="3"/>
+    <tableColumn id="4" name="uma_la" dataDxfId="2"/>
+    <tableColumn id="5" name="linea_complementaria" dataDxfId="1"/>
+    <tableColumn id="6" name="uma_lc" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5290,7 +5303,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2" s="58" t="s">
         <v>33</v>
       </c>
@@ -5313,7 +5326,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A3" s="58" t="s">
         <v>33</v>
       </c>
@@ -5336,7 +5349,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4" s="58" t="s">
         <v>40</v>
       </c>
@@ -5359,7 +5372,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A5" s="58" t="s">
         <v>40</v>
       </c>
@@ -5382,7 +5395,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A6" s="33" t="s">
         <v>33</v>
       </c>
@@ -5405,7 +5418,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7" s="33" t="s">
         <v>33</v>
       </c>
@@ -5428,7 +5441,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A8" s="58" t="s">
         <v>33</v>
       </c>
@@ -5451,7 +5464,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9" s="58" t="s">
         <v>33</v>
       </c>
@@ -5474,7 +5487,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10" s="58" t="s">
         <v>33</v>
       </c>
@@ -5497,7 +5510,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11" s="58" t="s">
         <v>33</v>
       </c>
@@ -5520,7 +5533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12" s="58" t="s">
         <v>33</v>
       </c>
@@ -5543,7 +5556,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A13" s="33" t="s">
         <v>40</v>
       </c>
@@ -5566,7 +5579,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14" s="33" t="s">
         <v>40</v>
       </c>
@@ -5589,7 +5602,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" s="58" t="s">
         <v>40</v>
       </c>
@@ -5612,7 +5625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16" s="58" t="s">
         <v>40</v>
       </c>
@@ -5635,7 +5648,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" s="58" t="s">
         <v>40</v>
       </c>
@@ -5658,7 +5671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" s="58" t="s">
         <v>40</v>
       </c>
@@ -5681,7 +5694,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" s="58" t="s">
         <v>40</v>
       </c>
@@ -5704,7 +5717,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" s="36" t="s">
         <v>33</v>
       </c>
@@ -5742,7 +5755,7 @@
       <c r="F21" s="29"/>
       <c r="G21" s="37"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" s="36" t="s">
         <v>33</v>
       </c>
@@ -5761,7 +5774,7 @@
       <c r="F22" s="29"/>
       <c r="G22" s="37"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23" s="36" t="s">
         <v>40</v>
       </c>
@@ -5780,7 +5793,7 @@
       <c r="F23" s="29"/>
       <c r="G23" s="37"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24" s="36" t="s">
         <v>34</v>
       </c>
@@ -5803,7 +5816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25" s="36" t="s">
         <v>34</v>
       </c>
@@ -5826,7 +5839,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" s="36" t="s">
         <v>34</v>
       </c>
@@ -5849,7 +5862,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" s="36" t="s">
         <v>34</v>
       </c>
@@ -5872,7 +5885,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A28" s="36" t="s">
         <v>34</v>
       </c>
@@ -5895,7 +5908,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29" s="36" t="s">
         <v>34</v>
       </c>
@@ -5918,7 +5931,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30" s="61" t="s">
         <v>34</v>
       </c>
@@ -5941,7 +5954,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" s="61" t="s">
         <v>34</v>
       </c>
@@ -5964,7 +5977,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32" s="61" t="s">
         <v>34</v>
       </c>
@@ -5987,7 +6000,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33" s="36" t="s">
         <v>40</v>
       </c>
@@ -6010,7 +6023,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A34" s="36" t="s">
         <v>40</v>
       </c>
@@ -6033,7 +6046,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A35" s="36" t="s">
         <v>40</v>
       </c>
@@ -6056,7 +6069,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A36" s="36" t="s">
         <v>40</v>
       </c>
@@ -6079,7 +6092,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37" s="36" t="s">
         <v>40</v>
       </c>
@@ -6102,7 +6115,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A38" s="36" t="s">
         <v>40</v>
       </c>
@@ -6125,7 +6138,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A39" s="61" t="s">
         <v>40</v>
       </c>
@@ -6148,7 +6161,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40" s="61" t="s">
         <v>40</v>
       </c>
@@ -6171,7 +6184,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A41" s="61" t="s">
         <v>40</v>
       </c>
@@ -6194,7 +6207,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" s="36" t="s">
         <v>33</v>
       </c>
@@ -6217,7 +6230,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" s="36" t="s">
         <v>33</v>
       </c>
@@ -6240,7 +6253,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A44" s="36" t="s">
         <v>33</v>
       </c>
@@ -6263,7 +6276,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A45" s="36" t="s">
         <v>33</v>
       </c>
@@ -6286,7 +6299,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A46" s="36" t="s">
         <v>33</v>
       </c>
@@ -6309,7 +6322,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A47" s="36" t="s">
         <v>33</v>
       </c>
@@ -6332,7 +6345,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A48" s="61" t="s">
         <v>33</v>
       </c>
@@ -6355,7 +6368,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A49" s="61" t="s">
         <v>33</v>
       </c>
@@ -6378,7 +6391,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50" s="61" t="s">
         <v>33</v>
       </c>

--- a/catalogos/CATALOGO_LINEAS_VALIDAS_21082026.xlsx
+++ b/catalogos/CATALOGO_LINEAS_VALIDAS_21082026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12570" tabRatio="635" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12570" tabRatio="635" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Adquisición" sheetId="3" r:id="rId1"/>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>Sustentabilidad</t>
-  </si>
-  <si>
-    <t>Reforzamiento estructural</t>
   </si>
   <si>
     <t>Obra preventiva</t>
@@ -173,6 +170,9 @@
   </si>
   <si>
     <t xml:space="preserve">Estudios y dictámenes </t>
+  </si>
+  <si>
+    <t>Reforzamiento estructural de la vivienda</t>
   </si>
 </sst>
 </file>
@@ -2439,6 +2439,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Tabla4" displayName="Tabla4" ref="A1:G14" totalsRowShown="0" headerRowDxfId="61" dataDxfId="60" tableBorderDxfId="59">
+  <autoFilter ref="A1:G14"/>
   <tableColumns count="7">
     <tableColumn id="1" name="esquema" dataDxfId="58"/>
     <tableColumn id="2" name="modalidad" dataDxfId="57"/>
@@ -2454,6 +2455,7 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabla3" displayName="Tabla3" ref="A1:G94" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
+  <autoFilter ref="A1:G94"/>
   <tableColumns count="7">
     <tableColumn id="1" name="esquema" dataDxfId="49"/>
     <tableColumn id="2" name="modalidad" dataDxfId="48"/>
@@ -2469,18 +2471,7 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Tabla1" displayName="Tabla1" ref="A1:G50" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41" tableBorderDxfId="39" totalsRowBorderDxfId="38">
-  <autoFilter ref="A1:G50">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Subsidio 100% CONAVI"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Adquisición de vivienda nueva"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:G50"/>
   <tableColumns count="7">
     <tableColumn id="1" name="esquema" dataDxfId="37"/>
     <tableColumn id="2" name="modalidad" dataDxfId="36"/>
@@ -2760,36 +2751,36 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="73" t="s">
+      <c r="C1" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="18" t="s">
+      <c r="G1" s="21" t="s">
         <v>35</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="21" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" s="38">
         <v>190</v>
@@ -2802,13 +2793,13 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" s="38">
         <v>170</v>
@@ -2821,13 +2812,13 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" s="72">
         <v>158</v>
@@ -2840,13 +2831,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="38">
         <v>140</v>
@@ -2859,13 +2850,13 @@
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>12</v>
-      </c>
       <c r="C6" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="38">
         <v>391</v>
@@ -2882,13 +2873,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>12</v>
-      </c>
       <c r="C7" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" s="38">
         <v>391</v>
@@ -2897,7 +2888,7 @@
         <v>140</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G7" s="13">
         <v>17</v>
@@ -2905,13 +2896,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>12</v>
-      </c>
       <c r="C8" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" s="38">
         <v>391</v>
@@ -2920,7 +2911,7 @@
         <v>140</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G8" s="13">
         <v>25</v>
@@ -2928,13 +2919,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>12</v>
-      </c>
       <c r="C9" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" s="38">
         <v>391</v>
@@ -2943,7 +2934,7 @@
         <v>140</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G9" s="13">
         <v>20</v>
@@ -2951,13 +2942,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>12</v>
-      </c>
       <c r="C10" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" s="38">
         <v>391</v>
@@ -2966,7 +2957,7 @@
         <v>140</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G10" s="13">
         <v>20</v>
@@ -2974,13 +2965,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>12</v>
-      </c>
       <c r="C11" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" s="38">
         <v>391</v>
@@ -2989,7 +2980,7 @@
         <v>140</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="13">
         <v>30</v>
@@ -2997,13 +2988,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>12</v>
-      </c>
       <c r="C12" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12" s="38">
         <v>391</v>
@@ -3020,13 +3011,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>12</v>
-      </c>
       <c r="C13" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13" s="38">
         <v>391</v>
@@ -3035,7 +3026,7 @@
         <v>140</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G13" s="13">
         <v>90</v>
@@ -3043,13 +3034,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>12</v>
-      </c>
       <c r="C14" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" s="38">
         <v>391</v>
@@ -3058,7 +3049,7 @@
         <v>140</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G14" s="13">
         <v>16</v>
@@ -3093,30 +3084,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="48" t="s">
+      <c r="D1" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="48" t="s">
+      <c r="G1" s="48" t="s">
         <v>35</v>
-      </c>
-      <c r="F1" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="48" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="29" t="s">
         <v>0</v>
@@ -3139,7 +3130,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="29" t="s">
         <v>0</v>
@@ -3162,7 +3153,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="29" t="s">
         <v>0</v>
@@ -3177,7 +3168,7 @@
         <v>25</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G4" s="32">
         <v>30</v>
@@ -3185,7 +3176,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="29" t="s">
         <v>0</v>
@@ -3200,7 +3191,7 @@
         <v>25</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="32">
         <v>30</v>
@@ -3208,7 +3199,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6" s="29" t="s">
         <v>0</v>
@@ -3223,7 +3214,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" s="32">
         <v>17</v>
@@ -3231,7 +3222,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="29" t="s">
         <v>0</v>
@@ -3246,7 +3237,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G7" s="32">
         <v>20</v>
@@ -3254,7 +3245,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" s="49" t="s">
         <v>0</v>
@@ -3269,7 +3260,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G8" s="52">
         <v>25</v>
@@ -3277,7 +3268,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="49" t="s">
         <v>0</v>
@@ -3292,7 +3283,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G9" s="52">
         <v>20</v>
@@ -3300,13 +3291,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10" s="44">
         <v>180</v>
@@ -3323,13 +3314,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D11" s="44">
         <v>180</v>
@@ -3346,13 +3337,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D12" s="44">
         <v>180</v>
@@ -3361,7 +3352,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="29" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G12" s="32">
         <v>30</v>
@@ -3369,13 +3360,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D13" s="44">
         <v>180</v>
@@ -3384,7 +3375,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" s="32">
         <v>30</v>
@@ -3392,13 +3383,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" s="44">
         <v>180</v>
@@ -3407,7 +3398,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G14" s="32">
         <v>17</v>
@@ -3415,13 +3406,13 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15" s="44">
         <v>180</v>
@@ -3430,7 +3421,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G15" s="32">
         <v>20</v>
@@ -3438,13 +3429,13 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B16" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D16" s="53">
         <v>180</v>
@@ -3453,7 +3444,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G16" s="52">
         <v>25</v>
@@ -3461,13 +3452,13 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" s="53">
         <v>180</v>
@@ -3476,7 +3467,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G17" s="52">
         <v>20</v>
@@ -3484,13 +3475,13 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18" s="53">
         <v>180</v>
@@ -3499,7 +3490,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G18" s="52">
         <v>16</v>
@@ -3507,13 +3498,13 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C19" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="44">
         <v>200</v>
@@ -3530,13 +3521,13 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="44">
         <v>200</v>
@@ -3553,13 +3544,13 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C21" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="44">
         <v>200</v>
@@ -3568,7 +3559,7 @@
         <v>100</v>
       </c>
       <c r="F21" s="29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" s="32">
         <v>30</v>
@@ -3576,13 +3567,13 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B22" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="44">
         <v>200</v>
@@ -3591,7 +3582,7 @@
         <v>100</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22" s="32">
         <v>17</v>
@@ -3599,13 +3590,13 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="44">
         <v>200</v>
@@ -3614,7 +3605,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G23" s="32">
         <v>20</v>
@@ -3622,13 +3613,13 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="53">
         <v>200</v>
@@ -3637,7 +3628,7 @@
         <v>100</v>
       </c>
       <c r="F24" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G24" s="52">
         <v>25</v>
@@ -3645,13 +3636,13 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="53">
         <v>200</v>
@@ -3660,7 +3651,7 @@
         <v>100</v>
       </c>
       <c r="F25" s="49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G25" s="52">
         <v>20</v>
@@ -3668,13 +3659,13 @@
     </row>
     <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="44">
         <v>187</v>
@@ -3691,13 +3682,13 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" s="44">
         <v>187</v>
@@ -3706,7 +3697,7 @@
         <v>100</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="32">
         <v>30</v>
@@ -3714,13 +3705,13 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" s="44">
         <v>187</v>
@@ -3729,7 +3720,7 @@
         <v>100</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="32">
         <v>17</v>
@@ -3737,13 +3728,13 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B29" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" s="44">
         <v>187</v>
@@ -3752,7 +3743,7 @@
         <v>100</v>
       </c>
       <c r="F29" s="29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G29" s="32">
         <v>20</v>
@@ -3760,13 +3751,13 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" s="53">
         <v>187</v>
@@ -3775,7 +3766,7 @@
         <v>100</v>
       </c>
       <c r="F30" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G30" s="52">
         <v>25</v>
@@ -3783,13 +3774,13 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" s="53">
         <v>187</v>
@@ -3798,7 +3789,7 @@
         <v>100</v>
       </c>
       <c r="F31" s="49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G31" s="52">
         <v>20</v>
@@ -3806,13 +3797,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D32" s="53">
         <v>187</v>
@@ -3821,7 +3812,7 @@
         <v>100</v>
       </c>
       <c r="F32" s="49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G32" s="52">
         <v>16</v>
@@ -3829,7 +3820,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" s="29" t="s">
         <v>0</v>
@@ -3852,7 +3843,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" s="29" t="s">
         <v>0</v>
@@ -3875,7 +3866,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B35" s="29" t="s">
         <v>0</v>
@@ -3890,7 +3881,7 @@
         <v>25</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G35" s="32">
         <v>30</v>
@@ -3898,7 +3889,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B36" s="29" t="s">
         <v>0</v>
@@ -3913,7 +3904,7 @@
         <v>25</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G36" s="32">
         <v>30</v>
@@ -3921,7 +3912,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" s="29" t="s">
         <v>0</v>
@@ -3936,7 +3927,7 @@
         <v>25</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G37" s="32">
         <v>17</v>
@@ -3944,7 +3935,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" s="29" t="s">
         <v>0</v>
@@ -3959,7 +3950,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G38" s="32">
         <v>20</v>
@@ -3967,7 +3958,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B39" s="49" t="s">
         <v>0</v>
@@ -3982,7 +3973,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G39" s="52">
         <v>25</v>
@@ -3990,7 +3981,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" s="49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B40" s="49" t="s">
         <v>0</v>
@@ -4005,7 +3996,7 @@
         <v>25</v>
       </c>
       <c r="F40" s="49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G40" s="52">
         <v>20</v>
@@ -4013,13 +4004,13 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B41" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D41" s="44">
         <v>180</v>
@@ -4036,13 +4027,13 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B42" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C42" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D42" s="44">
         <v>180</v>
@@ -4059,13 +4050,13 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B43" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D43" s="44">
         <v>180</v>
@@ -4074,7 +4065,7 @@
         <v>50</v>
       </c>
       <c r="F43" s="29" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G43" s="32">
         <v>30</v>
@@ -4082,13 +4073,13 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B44" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C44" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D44" s="44">
         <v>180</v>
@@ -4097,7 +4088,7 @@
         <v>50</v>
       </c>
       <c r="F44" s="29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G44" s="32">
         <v>30</v>
@@ -4105,13 +4096,13 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B45" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D45" s="44">
         <v>180</v>
@@ -4120,7 +4111,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G45" s="32">
         <v>17</v>
@@ -4128,13 +4119,13 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B46" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D46" s="44">
         <v>180</v>
@@ -4143,7 +4134,7 @@
         <v>50</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G46" s="32">
         <v>20</v>
@@ -4151,13 +4142,13 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" s="49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B47" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D47" s="53">
         <v>180</v>
@@ -4166,7 +4157,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G47" s="52">
         <v>25</v>
@@ -4174,13 +4165,13 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" s="49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B48" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D48" s="53">
         <v>180</v>
@@ -4189,7 +4180,7 @@
         <v>50</v>
       </c>
       <c r="F48" s="49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G48" s="52">
         <v>20</v>
@@ -4197,13 +4188,13 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" s="49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B49" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D49" s="53">
         <v>180</v>
@@ -4212,7 +4203,7 @@
         <v>50</v>
       </c>
       <c r="F49" s="49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G49" s="52">
         <v>16</v>
@@ -4220,13 +4211,13 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B50" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C50" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D50" s="44">
         <v>200</v>
@@ -4243,13 +4234,13 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B51" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C51" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D51" s="44">
         <v>200</v>
@@ -4266,13 +4257,13 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B52" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C52" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D52" s="44">
         <v>200</v>
@@ -4281,7 +4272,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G52" s="32">
         <v>30</v>
@@ -4289,13 +4280,13 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B53" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D53" s="44">
         <v>200</v>
@@ -4304,7 +4295,7 @@
         <v>100</v>
       </c>
       <c r="F53" s="29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G53" s="32">
         <v>17</v>
@@ -4312,13 +4303,13 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B54" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C54" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D54" s="44">
         <v>200</v>
@@ -4327,7 +4318,7 @@
         <v>100</v>
       </c>
       <c r="F54" s="29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G54" s="32">
         <v>20</v>
@@ -4335,13 +4326,13 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" s="49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B55" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D55" s="53">
         <v>200</v>
@@ -4350,7 +4341,7 @@
         <v>100</v>
       </c>
       <c r="F55" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G55" s="52">
         <v>25</v>
@@ -4358,13 +4349,13 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" s="49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B56" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D56" s="53">
         <v>200</v>
@@ -4373,7 +4364,7 @@
         <v>100</v>
       </c>
       <c r="F56" s="49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G56" s="52">
         <v>20</v>
@@ -4381,13 +4372,13 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B57" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D57" s="44">
         <v>187</v>
@@ -4404,13 +4395,13 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B58" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D58" s="44">
         <v>187</v>
@@ -4419,7 +4410,7 @@
         <v>100</v>
       </c>
       <c r="F58" s="29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G58" s="32">
         <v>30</v>
@@ -4427,13 +4418,13 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B59" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D59" s="44">
         <v>187</v>
@@ -4442,7 +4433,7 @@
         <v>100</v>
       </c>
       <c r="F59" s="29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G59" s="32">
         <v>17</v>
@@ -4450,13 +4441,13 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B60" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C60" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D60" s="44">
         <v>187</v>
@@ -4465,7 +4456,7 @@
         <v>100</v>
       </c>
       <c r="F60" s="29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G60" s="32">
         <v>20</v>
@@ -4473,13 +4464,13 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" s="49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B61" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D61" s="53">
         <v>187</v>
@@ -4488,7 +4479,7 @@
         <v>100</v>
       </c>
       <c r="F61" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G61" s="52">
         <v>25</v>
@@ -4496,13 +4487,13 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" s="49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B62" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D62" s="53">
         <v>187</v>
@@ -4511,7 +4502,7 @@
         <v>100</v>
       </c>
       <c r="F62" s="49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G62" s="52">
         <v>20</v>
@@ -4519,13 +4510,13 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" s="49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B63" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D63" s="53">
         <v>187</v>
@@ -4534,7 +4525,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G63" s="52">
         <v>16</v>
@@ -4542,7 +4533,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B64" s="29" t="s">
         <v>0</v>
@@ -4565,7 +4556,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A65" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B65" s="29" t="s">
         <v>0</v>
@@ -4588,7 +4579,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A66" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B66" s="29" t="s">
         <v>0</v>
@@ -4603,7 +4594,7 @@
         <v>25</v>
       </c>
       <c r="F66" s="29" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G66" s="32">
         <v>30</v>
@@ -4611,7 +4602,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A67" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B67" s="29" t="s">
         <v>0</v>
@@ -4626,7 +4617,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G67" s="32">
         <v>30</v>
@@ -4634,7 +4625,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A68" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B68" s="29" t="s">
         <v>0</v>
@@ -4649,7 +4640,7 @@
         <v>25</v>
       </c>
       <c r="F68" s="29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G68" s="32">
         <v>17</v>
@@ -4657,7 +4648,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A69" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B69" s="29" t="s">
         <v>0</v>
@@ -4672,7 +4663,7 @@
         <v>25</v>
       </c>
       <c r="F69" s="29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G69" s="32">
         <v>20</v>
@@ -4680,7 +4671,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A70" s="49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B70" s="49" t="s">
         <v>0</v>
@@ -4695,7 +4686,7 @@
         <v>25</v>
       </c>
       <c r="F70" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G70" s="52">
         <v>25</v>
@@ -4703,7 +4694,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A71" s="49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B71" s="49" t="s">
         <v>0</v>
@@ -4718,7 +4709,7 @@
         <v>25</v>
       </c>
       <c r="F71" s="49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G71" s="52">
         <v>20</v>
@@ -4726,13 +4717,13 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A72" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B72" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C72" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D72" s="44">
         <v>180</v>
@@ -4749,13 +4740,13 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A73" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B73" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C73" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D73" s="44">
         <v>180</v>
@@ -4772,13 +4763,13 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A74" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B74" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C74" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D74" s="44">
         <v>180</v>
@@ -4787,7 +4778,7 @@
         <v>50</v>
       </c>
       <c r="F74" s="29" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G74" s="32">
         <v>30</v>
@@ -4795,13 +4786,13 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A75" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B75" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C75" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D75" s="44">
         <v>180</v>
@@ -4810,7 +4801,7 @@
         <v>50</v>
       </c>
       <c r="F75" s="29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G75" s="32">
         <v>30</v>
@@ -4818,13 +4809,13 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A76" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B76" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C76" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D76" s="44">
         <v>180</v>
@@ -4833,7 +4824,7 @@
         <v>50</v>
       </c>
       <c r="F76" s="29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G76" s="32">
         <v>17</v>
@@ -4841,13 +4832,13 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A77" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B77" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C77" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D77" s="44">
         <v>180</v>
@@ -4856,7 +4847,7 @@
         <v>50</v>
       </c>
       <c r="F77" s="29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G77" s="32">
         <v>20</v>
@@ -4864,13 +4855,13 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A78" s="49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B78" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D78" s="53">
         <v>180</v>
@@ -4879,7 +4870,7 @@
         <v>50</v>
       </c>
       <c r="F78" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G78" s="52">
         <v>25</v>
@@ -4887,13 +4878,13 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A79" s="49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B79" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D79" s="53">
         <v>180</v>
@@ -4902,7 +4893,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G79" s="52">
         <v>20</v>
@@ -4910,13 +4901,13 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A80" s="49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B80" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D80" s="53">
         <v>180</v>
@@ -4925,7 +4916,7 @@
         <v>50</v>
       </c>
       <c r="F80" s="49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G80" s="52">
         <v>16</v>
@@ -4933,13 +4924,13 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B81" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C81" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D81" s="44">
         <v>200</v>
@@ -4956,13 +4947,13 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A82" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B82" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C82" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D82" s="44">
         <v>200</v>
@@ -4979,13 +4970,13 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A83" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B83" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C83" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D83" s="44">
         <v>200</v>
@@ -4994,7 +4985,7 @@
         <v>100</v>
       </c>
       <c r="F83" s="29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G83" s="32">
         <v>30</v>
@@ -5002,13 +4993,13 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A84" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B84" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C84" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D84" s="44">
         <v>200</v>
@@ -5017,7 +5008,7 @@
         <v>100</v>
       </c>
       <c r="F84" s="29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G84" s="32">
         <v>17</v>
@@ -5025,13 +5016,13 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A85" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B85" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C85" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D85" s="44">
         <v>200</v>
@@ -5040,7 +5031,7 @@
         <v>100</v>
       </c>
       <c r="F85" s="29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G85" s="32">
         <v>20</v>
@@ -5048,13 +5039,13 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A86" s="49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B86" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C86" s="50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D86" s="53">
         <v>200</v>
@@ -5063,7 +5054,7 @@
         <v>100</v>
       </c>
       <c r="F86" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G86" s="52">
         <v>25</v>
@@ -5071,13 +5062,13 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A87" s="49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B87" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C87" s="50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D87" s="53">
         <v>200</v>
@@ -5086,7 +5077,7 @@
         <v>100</v>
       </c>
       <c r="F87" s="49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G87" s="52">
         <v>20</v>
@@ -5094,13 +5085,13 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A88" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B88" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C88" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D88" s="44">
         <v>187</v>
@@ -5117,13 +5108,13 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A89" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B89" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C89" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D89" s="44">
         <v>187</v>
@@ -5132,7 +5123,7 @@
         <v>100</v>
       </c>
       <c r="F89" s="29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G89" s="32">
         <v>30</v>
@@ -5140,13 +5131,13 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A90" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B90" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C90" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D90" s="44">
         <v>187</v>
@@ -5155,7 +5146,7 @@
         <v>100</v>
       </c>
       <c r="F90" s="29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G90" s="32">
         <v>17</v>
@@ -5163,13 +5154,13 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A91" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B91" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C91" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D91" s="44">
         <v>187</v>
@@ -5178,7 +5169,7 @@
         <v>100</v>
       </c>
       <c r="F91" s="29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G91" s="32">
         <v>20</v>
@@ -5186,13 +5177,13 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A92" s="49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B92" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D92" s="53">
         <v>187</v>
@@ -5201,7 +5192,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G92" s="52">
         <v>25</v>
@@ -5209,13 +5200,13 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A93" s="49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B93" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C93" s="50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D93" s="53">
         <v>187</v>
@@ -5224,7 +5215,7 @@
         <v>100</v>
       </c>
       <c r="F93" s="49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G93" s="52">
         <v>20</v>
@@ -5232,13 +5223,13 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A94" s="49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B94" s="49" t="s">
         <v>0</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D94" s="53">
         <v>187</v>
@@ -5247,7 +5238,7 @@
         <v>100</v>
       </c>
       <c r="F94" s="49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G94" s="52">
         <v>16</v>
@@ -5282,36 +5273,36 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="39" x14ac:dyDescent="0.45">
       <c r="A1" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="C1" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="55" t="s">
+      <c r="D1" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="55" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="55" t="s">
+      <c r="G1" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="56" t="s">
+    </row>
+    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="57" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="58" t="s">
-        <v>33</v>
-      </c>
       <c r="B2" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" s="59">
         <v>86</v>
@@ -5320,21 +5311,21 @@
         <v>86</v>
       </c>
       <c r="F2" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G2" s="60">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A3" s="58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" s="50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="59">
         <v>86</v>
@@ -5343,21 +5334,21 @@
         <v>86</v>
       </c>
       <c r="F3" s="49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G3" s="52">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" s="50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="59">
         <v>86</v>
@@ -5366,21 +5357,21 @@
         <v>86</v>
       </c>
       <c r="F4" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G4" s="60">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="59">
         <v>86</v>
@@ -5389,21 +5380,21 @@
         <v>86</v>
       </c>
       <c r="F5" s="49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G5" s="52">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="31">
         <v>150</v>
@@ -5418,15 +5409,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="31">
         <v>150</v>
@@ -5435,21 +5426,21 @@
         <v>100</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7" s="37">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="51">
         <v>150</v>
@@ -5464,15 +5455,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="51">
         <v>150</v>
@@ -5481,21 +5472,21 @@
         <v>100</v>
       </c>
       <c r="F9" s="50" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9" s="60">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="51">
         <v>150</v>
@@ -5504,21 +5495,21 @@
         <v>100</v>
       </c>
       <c r="F10" s="50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G10" s="60">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="51">
         <v>150</v>
@@ -5527,21 +5518,21 @@
         <v>100</v>
       </c>
       <c r="F11" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G11" s="60">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="51">
         <v>150</v>
@@ -5550,21 +5541,21 @@
         <v>100</v>
       </c>
       <c r="F12" s="50" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G12" s="60">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="31">
         <v>150</v>
@@ -5579,15 +5570,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="31">
         <v>150</v>
@@ -5596,21 +5587,21 @@
         <v>100</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" s="37">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="51">
         <v>150</v>
@@ -5625,15 +5616,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B16" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="51">
         <v>150</v>
@@ -5642,21 +5633,21 @@
         <v>100</v>
       </c>
       <c r="F16" s="50" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" s="60">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="51">
         <v>150</v>
@@ -5665,21 +5656,21 @@
         <v>100</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G17" s="60">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="51">
         <v>150</v>
@@ -5688,21 +5679,21 @@
         <v>100</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G18" s="60">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="51">
         <v>150</v>
@@ -5711,21 +5702,21 @@
         <v>100</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G19" s="60">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D20" s="31">
         <v>170</v>
@@ -5738,13 +5729,13 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21" s="30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D21" s="31">
         <v>170</v>
@@ -5755,15 +5746,15 @@
       <c r="F21" s="29"/>
       <c r="G21" s="37"/>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22" s="31">
         <v>140</v>
@@ -5774,15 +5765,15 @@
       <c r="F22" s="29"/>
       <c r="G22" s="37"/>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D23" s="31">
         <v>140</v>
@@ -5793,15 +5784,15 @@
       <c r="F23" s="29"/>
       <c r="G23" s="37"/>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D24" s="34">
         <v>330</v>
@@ -5816,15 +5807,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D25" s="34">
         <v>330</v>
@@ -5839,15 +5830,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D26" s="34">
         <v>330</v>
@@ -5856,21 +5847,21 @@
         <v>140</v>
       </c>
       <c r="F26" s="29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" s="37">
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D27" s="34">
         <v>330</v>
@@ -5879,21 +5870,21 @@
         <v>140</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G27" s="37">
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D28" s="34">
         <v>330</v>
@@ -5902,21 +5893,21 @@
         <v>140</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G28" s="37">
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D29" s="34">
         <v>330</v>
@@ -5925,21 +5916,21 @@
         <v>140</v>
       </c>
       <c r="F29" s="29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G29" s="37">
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30" s="62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D30" s="59">
         <v>330</v>
@@ -5948,21 +5939,21 @@
         <v>140</v>
       </c>
       <c r="F30" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G30" s="52">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C31" s="62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D31" s="59">
         <v>330</v>
@@ -5971,21 +5962,21 @@
         <v>140</v>
       </c>
       <c r="F31" s="49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G31" s="52">
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B32" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C32" s="62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D32" s="59">
         <v>330</v>
@@ -5994,21 +5985,21 @@
         <v>140</v>
       </c>
       <c r="F32" s="49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G32" s="52">
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D33" s="34">
         <v>330</v>
@@ -6023,15 +6014,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D34" s="34">
         <v>330</v>
@@ -6046,15 +6037,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D35" s="34">
         <v>330</v>
@@ -6063,21 +6054,21 @@
         <v>140</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G35" s="37">
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D36" s="34">
         <v>330</v>
@@ -6086,21 +6077,21 @@
         <v>140</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G36" s="37">
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D37" s="34">
         <v>330</v>
@@ -6109,21 +6100,21 @@
         <v>140</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G37" s="37">
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D38" s="34">
         <v>330</v>
@@ -6132,21 +6123,21 @@
         <v>140</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G38" s="37">
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C39" s="62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D39" s="59">
         <v>330</v>
@@ -6155,21 +6146,21 @@
         <v>140</v>
       </c>
       <c r="F39" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G39" s="52">
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" s="61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C40" s="62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D40" s="59">
         <v>330</v>
@@ -6178,21 +6169,21 @@
         <v>140</v>
       </c>
       <c r="F40" s="49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G40" s="52">
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" s="61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C41" s="62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D41" s="59">
         <v>330</v>
@@ -6201,21 +6192,21 @@
         <v>140</v>
       </c>
       <c r="F41" s="49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G41" s="52">
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" s="36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D42" s="32">
         <v>330</v>
@@ -6230,15 +6221,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" s="36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B43" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D43" s="32">
         <v>330</v>
@@ -6253,15 +6244,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" s="36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B44" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D44" s="32">
         <v>330</v>
@@ -6270,21 +6261,21 @@
         <v>140</v>
       </c>
       <c r="F44" s="29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G44" s="37">
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" s="36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B45" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D45" s="32">
         <v>330</v>
@@ -6293,21 +6284,21 @@
         <v>140</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G45" s="37">
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" s="36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B46" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D46" s="32">
         <v>330</v>
@@ -6316,21 +6307,21 @@
         <v>140</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G46" s="37">
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" s="36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B47" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C47" s="45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D47" s="46">
         <v>330</v>
@@ -6339,21 +6330,21 @@
         <v>140</v>
       </c>
       <c r="F47" s="45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G47" s="64">
         <v>90</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" s="61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B48" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C48" s="65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D48" s="71">
         <v>330</v>
@@ -6362,21 +6353,21 @@
         <v>140</v>
       </c>
       <c r="F48" s="67" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G48" s="68">
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" s="61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B49" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C49" s="65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D49" s="71">
         <v>330</v>
@@ -6385,21 +6376,21 @@
         <v>140</v>
       </c>
       <c r="F49" s="67" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G49" s="68">
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" s="61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B50" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C50" s="65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D50" s="71">
         <v>330</v>
@@ -6408,7 +6399,7 @@
         <v>140</v>
       </c>
       <c r="F50" s="69" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G50" s="70">
         <v>16</v>
@@ -6443,36 +6434,36 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>35</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" s="13">
         <v>330</v>
@@ -6481,7 +6472,7 @@
         <v>270</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" s="13">
         <v>30</v>
@@ -6489,13 +6480,13 @@
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A3" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" s="13">
         <v>330</v>
@@ -6504,7 +6495,7 @@
         <v>270</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G3" s="13">
         <v>30</v>
@@ -6512,13 +6503,13 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" s="13">
         <v>330</v>
@@ -6527,7 +6518,7 @@
         <v>270</v>
       </c>
       <c r="F4" s="42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G4" s="13">
         <v>20</v>
@@ -6535,13 +6526,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="13">
         <v>330</v>
@@ -6550,7 +6541,7 @@
         <v>270</v>
       </c>
       <c r="F5" s="42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G5" s="13">
         <v>16</v>
@@ -6558,13 +6549,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" s="13">
         <v>180</v>
@@ -6581,13 +6572,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" s="13">
         <v>180</v>
@@ -6604,13 +6595,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="13">
         <v>180</v>
@@ -6619,7 +6610,7 @@
         <v>50</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G8" s="19">
         <v>30</v>
@@ -6627,13 +6618,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" s="13">
         <v>180</v>
@@ -6642,7 +6633,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" s="19">
         <v>30</v>
@@ -6650,13 +6641,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10" s="13">
         <v>180</v>
@@ -6665,7 +6656,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" s="19">
         <v>17</v>
@@ -6673,13 +6664,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="13">
         <v>180</v>
@@ -6688,7 +6679,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G11" s="19">
         <v>20</v>
@@ -6696,13 +6687,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" s="13">
         <v>180</v>
@@ -6711,7 +6702,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G12" s="19">
         <v>25</v>
@@ -6719,13 +6710,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13" s="13">
         <v>180</v>
@@ -6734,7 +6725,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G13" s="19">
         <v>20</v>
@@ -6742,13 +6733,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" s="13">
         <v>180</v>
@@ -6757,7 +6748,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G14" s="19">
         <v>16</v>
@@ -6765,13 +6756,13 @@
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" s="13">
         <v>200</v>
@@ -6788,13 +6779,13 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" s="13">
         <v>200</v>
@@ -6811,13 +6802,13 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D17" s="13">
         <v>200</v>
@@ -6826,7 +6817,7 @@
         <v>100</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G17" s="19">
         <v>30</v>
@@ -6834,13 +6825,13 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D18" s="13">
         <v>200</v>
@@ -6849,7 +6840,7 @@
         <v>100</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" s="19">
         <v>17</v>
@@ -6857,13 +6848,13 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" s="13">
         <v>200</v>
@@ -6872,7 +6863,7 @@
         <v>100</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G19" s="19">
         <v>20</v>
@@ -6880,13 +6871,13 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D20" s="13">
         <v>200</v>
@@ -6895,7 +6886,7 @@
         <v>100</v>
       </c>
       <c r="F20" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G20" s="19">
         <v>25</v>
@@ -6903,13 +6894,13 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D21" s="13">
         <v>200</v>
@@ -6918,7 +6909,7 @@
         <v>100</v>
       </c>
       <c r="F21" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G21" s="19">
         <v>20</v>
@@ -6926,13 +6917,13 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" s="13">
         <v>200</v>
@@ -6941,7 +6932,7 @@
         <v>100</v>
       </c>
       <c r="F22" s="43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G22" s="19">
         <v>16</v>
@@ -6949,13 +6940,13 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="13">
         <v>162</v>
@@ -6972,13 +6963,13 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="13">
         <v>162</v>
@@ -6987,7 +6978,7 @@
         <v>75</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G24" s="19">
         <v>30</v>
@@ -6995,13 +6986,13 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="13">
         <v>162</v>
@@ -7010,7 +7001,7 @@
         <v>75</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G25" s="19">
         <v>17</v>
@@ -7018,13 +7009,13 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="13">
         <v>162</v>
@@ -7033,7 +7024,7 @@
         <v>75</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G26" s="19">
         <v>20</v>
@@ -7041,13 +7032,13 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" s="13">
         <v>162</v>
@@ -7056,7 +7047,7 @@
         <v>75</v>
       </c>
       <c r="F27" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G27" s="19">
         <v>25</v>
@@ -7064,13 +7055,13 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" s="13">
         <v>162</v>
@@ -7079,7 +7070,7 @@
         <v>75</v>
       </c>
       <c r="F28" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G28" s="19">
         <v>20</v>
@@ -7087,13 +7078,13 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" s="13">
         <v>162</v>
@@ -7102,7 +7093,7 @@
         <v>75</v>
       </c>
       <c r="F29" s="43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G29" s="19">
         <v>16</v>
@@ -7110,13 +7101,13 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D30" s="19">
         <v>330</v>
@@ -7125,7 +7116,7 @@
         <v>270</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" s="19">
         <v>30</v>
@@ -7133,13 +7124,13 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D31" s="19">
         <v>330</v>
@@ -7148,7 +7139,7 @@
         <v>270</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G31" s="19">
         <v>30</v>
@@ -7156,13 +7147,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D32" s="13">
         <v>330</v>
@@ -7171,7 +7162,7 @@
         <v>270</v>
       </c>
       <c r="F32" s="42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G32" s="13">
         <v>20</v>
@@ -7179,13 +7170,13 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D33" s="13">
         <v>330</v>
@@ -7194,7 +7185,7 @@
         <v>270</v>
       </c>
       <c r="F33" s="42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G33" s="13">
         <v>16</v>
@@ -7202,13 +7193,13 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D34" s="19">
         <v>180</v>
@@ -7225,13 +7216,13 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D35" s="19">
         <v>180</v>
@@ -7248,13 +7239,13 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D36" s="19">
         <v>180</v>
@@ -7263,7 +7254,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G36" s="19">
         <v>30</v>
@@ -7271,13 +7262,13 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D37" s="19">
         <v>180</v>
@@ -7286,7 +7277,7 @@
         <v>50</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G37" s="19">
         <v>30</v>
@@ -7294,13 +7285,13 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D38" s="19">
         <v>180</v>
@@ -7309,7 +7300,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G38" s="19">
         <v>17</v>
@@ -7317,13 +7308,13 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D39" s="19">
         <v>180</v>
@@ -7332,7 +7323,7 @@
         <v>50</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G39" s="19">
         <v>20</v>
@@ -7340,13 +7331,13 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D40" s="19">
         <v>180</v>
@@ -7355,7 +7346,7 @@
         <v>50</v>
       </c>
       <c r="F40" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G40" s="19">
         <v>25</v>
@@ -7363,13 +7354,13 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D41" s="19">
         <v>180</v>
@@ -7378,7 +7369,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G41" s="19">
         <v>20</v>
@@ -7386,13 +7377,13 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D42" s="19">
         <v>180</v>
@@ -7401,7 +7392,7 @@
         <v>50</v>
       </c>
       <c r="F42" s="43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G42" s="19">
         <v>16</v>
@@ -7409,13 +7400,13 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D43" s="19">
         <v>200</v>
@@ -7432,13 +7423,13 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D44" s="19">
         <v>200</v>
@@ -7455,13 +7446,13 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D45" s="19">
         <v>200</v>
@@ -7470,7 +7461,7 @@
         <v>100</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G45" s="19">
         <v>30</v>
@@ -7478,13 +7469,13 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D46" s="19">
         <v>200</v>
@@ -7493,7 +7484,7 @@
         <v>100</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G46" s="19">
         <v>17</v>
@@ -7501,13 +7492,13 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D47" s="19">
         <v>200</v>
@@ -7516,7 +7507,7 @@
         <v>100</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G47" s="19">
         <v>20</v>
@@ -7524,13 +7515,13 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D48" s="13">
         <v>200</v>
@@ -7539,7 +7530,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G48" s="19">
         <v>25</v>
@@ -7547,13 +7538,13 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D49" s="13">
         <v>200</v>
@@ -7562,7 +7553,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G49" s="19">
         <v>20</v>
@@ -7570,13 +7561,13 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D50" s="13">
         <v>200</v>
@@ -7585,7 +7576,7 @@
         <v>100</v>
       </c>
       <c r="F50" s="43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G50" s="19">
         <v>16</v>
@@ -7593,13 +7584,13 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D51" s="13">
         <v>162</v>
@@ -7616,13 +7607,13 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D52" s="13">
         <v>162</v>
@@ -7631,7 +7622,7 @@
         <v>75</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G52" s="19">
         <v>30</v>
@@ -7639,13 +7630,13 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D53" s="13">
         <v>162</v>
@@ -7654,7 +7645,7 @@
         <v>75</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G53" s="19">
         <v>17</v>
@@ -7662,13 +7653,13 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D54" s="13">
         <v>162</v>
@@ -7677,7 +7668,7 @@
         <v>75</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G54" s="19">
         <v>20</v>
@@ -7685,13 +7676,13 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D55" s="13">
         <v>162</v>
@@ -7700,7 +7691,7 @@
         <v>75</v>
       </c>
       <c r="F55" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G55" s="19">
         <v>25</v>
@@ -7708,13 +7699,13 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D56" s="13">
         <v>162</v>
@@ -7723,7 +7714,7 @@
         <v>75</v>
       </c>
       <c r="F56" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G56" s="19">
         <v>20</v>
@@ -7731,13 +7722,13 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D57" s="13">
         <v>162</v>
@@ -7746,7 +7737,7 @@
         <v>75</v>
       </c>
       <c r="F57" s="43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G57" s="19">
         <v>16</v>
@@ -7780,36 +7771,36 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="G1" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" s="41">
         <v>25</v>
@@ -7848,36 +7839,36 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="G1" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" s="38">
         <v>14</v>
@@ -7894,13 +7885,13 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="39">
         <v>14</v>
